--- a/files/九龙-启德-维港．双钻.xlsx
+++ b/files/九龙-启德-维港．双钻.xlsx
@@ -8,6 +8,10 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1A座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1B座" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2A座" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2B座" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +45,107 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +156,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +221,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +237,66 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +673,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -33637,4 +33836,6884 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1A座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 493呎 (2房)
+$1040万
+$21,089/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 305呎 (1房)
+$589万
+$19,311/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 305呎 (1房)
+$596万
+$19,525/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+$638万
+$20,925/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>E | 301呎 (1房)
+$638万
+$21,196/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G5" s="21" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$1090万
+$24,376/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>G | 437呎 (2房)
+$883万
+$20,208/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 493呎 (2房)
+$1018万
+$20,643/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 305呎 (1房)
+$583万
+$19,121/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 305呎 (1房)
+$590万
+$19,328/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+$596万
+$19,541/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>E | 301呎 (1房)
+$625万
+$20,754/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$1079万
+$24,134/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>G | 437呎 (2房)
+$874万
+$20,007/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 493呎 (2房)
+$1008万
+$20,440/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 305呎 (1房)
+$577万
+$18,931/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 305呎 (1房)
+$584万
+$19,138/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+$590万
+$19,348/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>E | 301呎 (1房)
+$619万
+$20,551/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G7" s="21" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$1068万
+$23,897/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>G | 437呎 (2房)
+$866万
+$19,810/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 493呎 (2房)
+$998万
+$20,237/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 305呎 (1房)
+$578万
+$18,954/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>C | 305呎 (1房)
+$578万
+$18,951/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+$584万
+$19,154/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>E | 301呎 (1房)
+$610万
+$20,249/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G8" s="21" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$1058万
+$23,660/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>G | 437呎 (2房)
+$867万
+$19,844/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 493呎 (2房)
+$988万
+$20,034/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 305呎 (1房)
+$572万
+$18,764/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 305呎 (1房)
+$572万
+$18,761/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+$578万
+$18,967/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>E | 301呎 (1房)
+$604万
+$20,050/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G9" s="21" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$1047万
+$23,425/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>G | 437呎 (2房)
+$849万
+$19,421/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 493呎 (2房)
+$983万
+$19,935/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 305呎 (1房)
+$569万
+$18,669/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 305呎 (1房)
+$569万
+$18,669/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+$576万
+$18,872/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>E | 301呎 (1房)
+$607万
+$20,169/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$909万
+$20,338/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>G | 437呎 (2房)
+$844万
+$19,323/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 493呎 (2房)
+$978万
+$19,838/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 305呎 (1房)
+$567万
+$18,577/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 305呎 (1房)
+$567万
+$18,577/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+$573万
+$18,777/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>E | 301呎 (1房)
+$598万
+$19,854/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$905万
+$20,237/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="inlineStr">
+        <is>
+          <t>G | 437呎 (2房)
+$860万
+$19,682/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>A | 493呎 (2房)
+$1122万
+$22,753/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>B | 305呎 (1房)
+$620万
+$20,311/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>C | 305呎 (1房)
+$626万
+$20,534/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+$633万
+$20,754/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t>E | 301呎 (1房)
+$631万
+$20,963/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H12" s="22" t="inlineStr">
+        <is>
+          <t>G | 437呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 493呎 (2房)
+$968万
+$19,641/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 305呎 (1房)
+$561万
+$18,393/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C | 305呎 (1房)
+$561万
+$18,390/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+$567万
+$18,590/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>E | 301呎 (1房)
+$592万
+$19,654/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$896万
+$20,036/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H13" s="20" t="inlineStr">
+        <is>
+          <t>G | 437呎 (2房)
+$852万
+$19,485/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 493呎 (2房)
+$963万
+$19,542/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 305呎 (1房)
+$558万
+$18,302/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 305呎 (1房)
+$558万
+$18,298/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+$564万
+$18,502/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>E | 301呎 (1房)
+$614万
+$20,402/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$891万
+$19,935/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H14" s="20" t="inlineStr">
+        <is>
+          <t>G | 437呎 (2房)
+$828万
+$18,941/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 493呎 (2房)
+$959万
+$19,444/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 305呎 (1房)
+$568万
+$18,610/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>C | 305呎 (1房)
+$555万
+$18,207/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+$561万
+$18,407/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>E | 301呎 (1房)
+$586万
+$19,458/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G15" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$887万
+$19,837/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H15" s="20" t="inlineStr">
+        <is>
+          <t>G | 437呎 (2房)
+$824万
+$18,849/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 493呎 (2房)
+$954万
+$19,349/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 305呎 (1房)
+$556万
+$18,216/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>C | 305呎 (1房)
+$553万
+$18,118/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+$559万
+$18,315/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>E | 301呎 (1房)
+$583万
+$19,362/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$882万
+$19,738/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H16" s="20" t="inlineStr">
+        <is>
+          <t>G | 437呎 (2房)
+$820万
+$18,753/呎
+(25年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 493呎 (2房)
+$949万
+$19,252/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 305呎 (1房)
+$553万
+$18,128/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 305呎 (1房)
+$550万
+$18,030/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+$556万
+$18,223/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>E | 301呎 (1房)
+$577万
+$19,173/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$878万
+$19,640/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>G | 437呎 (2房)
+$815万
+$18,659/呎
+(25年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 493呎 (2房)
+$933万
+$18,933/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 305呎 (1房)
+$550万
+$18,036/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 305呎 (1房)
+$547万
+$17,938/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+$553万
+$18,131/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>E | 301呎 (1房)
+$574万
+$19,073/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G18" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$863万
+$19,315/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H18" s="20" t="inlineStr">
+        <is>
+          <t>G | 437呎 (2房)
+$802万
+$18,348/呎
+(25年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 493呎 (2房)
+$929万
+$18,838/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 305呎 (1房)
+$538万
+$17,652/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>C | 305呎 (1房)
+$544万
+$17,846/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+$550万
+$18,043/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>E | 301呎 (1房)
+$571万
+$18,980/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G19" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$859万
+$19,219/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="H19" s="20" t="inlineStr">
+        <is>
+          <t>G | 437呎 (2房)
+$798万
+$18,256/呎
+(25年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 493呎 (2房)
+$924万
+$18,744/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 305呎 (1房)
+$536万
+$17,564/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>C | 305呎 (1房)
+$542万
+$17,757/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+$548万
+$17,951/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>E | 301呎 (1房)
+$568万
+$18,884/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G20" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$855万
+$19,123/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H20" s="20" t="inlineStr">
+        <is>
+          <t>G | 437呎 (2房)
+$794万
+$18,162/呎
+(25年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 493呎 (2房)
+$920万
+$18,651/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 305呎 (1房)
+$533万
+$17,475/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>C | 305呎 (1房)
+$539万
+$17,669/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+$557万
+$18,259/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>E | 301呎 (1房)
+$560万
+$18,608/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G21" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$851万
+$19,029/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H21" s="23" t="inlineStr">
+        <is>
+          <t>G | 437呎 (2房)
+$943万
+$21,577/呎
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 493呎 (2房)
+$909万
+$18,442/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 305呎 (1房)
+$529万
+$17,351/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>C | 305呎 (1房)
+$535万
+$17,544/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+$541万
+$17,734/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>E | 301呎 (1房)
+$556万
+$18,475/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G22" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$850万
+$19,007/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H22" s="20" t="inlineStr">
+        <is>
+          <t>G | 437呎 (2房)
+$789万
+$18,055/呎
+(25年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 493呎 (2房)
+$905万
+$18,357/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 305呎 (1房)
+$526万
+$17,233/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>C | 305呎 (1房)
+$531万
+$17,423/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+$537万
+$17,613/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>E | 301呎 (1房)
+$552万
+$18,346/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G23" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$849万
+$18,998/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="H23" s="20" t="inlineStr">
+        <is>
+          <t>G | 437呎 (2房)
+$786万
+$17,995/呎
+(25年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 493呎 (2房)
+$898万
+$18,207/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>B | 305呎 (1房)
+$522万
+$17,111/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>C | 305呎 (1房)
+$528万
+$17,302/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+$533万
+$17,489/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="F24" s="20" t="inlineStr">
+        <is>
+          <t>E | 301呎 (1房)
+$548万
+$18,219/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G24" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$840万
+$18,792/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H24" s="20" t="inlineStr">
+        <is>
+          <t>G | 437呎 (2房)
+$780万
+$17,854/呎
+(25年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>A | 493呎 (2房)
+$885万
+$17,955/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>B | 305呎 (1房)
+$518万
+$16,990/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>C | 305呎 (1房)
+$524万
+$17,180/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+$530万
+$17,367/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
+        <is>
+          <t>E | 301呎 (1房)
+$540万
+$17,930/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G25" s="20" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+$826万
+$18,479/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
+        <is>
+          <t>G | 437呎 (2房)
+$767万
+$17,556/呎
+(25年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>A | 493呎 (2房)
+$876万
+$17,779/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>B | 305呎 (1房)
+$515万
+$16,872/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>C | 305呎 (1房)
+$520万
+$17,056/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+$529万
+$17,341/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="F26" s="20" t="inlineStr">
+        <is>
+          <t>E | 301呎 (1房)
+$530万
+$17,611/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G26" s="24" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="H26" s="20" t="inlineStr">
+        <is>
+          <t>G | 437呎 (2房)
+$757万
+$17,327/呎
+(25年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>A | 493呎 (2房)
+$854万
+$17,312/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>B | 305呎 (1房)
+$514万
+$16,846/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>C | 305呎 (1房)
+$520万
+$17,033/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+$531万
+$17,410/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="inlineStr">
+        <is>
+          <t>E | 301呎 (1房)
+$526万
+$17,488/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G27" s="24" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="H27" s="20" t="inlineStr">
+        <is>
+          <t>G | 437呎 (2房)
+$746万
+$17,071/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>A | 493呎 (2房)
+$838万
+$17,008/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>B | 305呎 (1房)
+$513万
+$16,820/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>C | 305呎 (1房)
+$519万
+$17,007/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+$524万
+$17,193/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F28" s="20" t="inlineStr">
+        <is>
+          <t>E | 301呎 (1房)
+$523万
+$17,369/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G28" s="24" t="inlineStr">
+        <is>
+          <t>F | 447呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="H28" s="20" t="inlineStr">
+        <is>
+          <t>G | 437呎 (2房)
+$733万
+$16,767/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1B座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 440呎 (2房)
+$1072万
+$24,361/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C5" s="22" t="inlineStr">
+        <is>
+          <t>B | 447呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>C | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 245呎 (开放式)
+$554万
+$22,604/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>E | 246呎 (开放式)
+$474万
+$19,252/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>F | 246呎 (开放式)
+$476万
+$19,362/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>G | 300呎 (1房)
+$583万
+$19,427/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="I5" s="24" t="inlineStr">
+        <is>
+          <t>H | 493呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 440呎 (2房)
+$907万
+$20,620/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 447呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>C | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>D | 245呎 (开放式)
+$487万
+$19,890/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>E | 246呎 (开放式)
+$469万
+$19,061/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>F | 246呎 (开放式)
+$472万
+$19,167/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>G | 300呎 (1房)
+$577万
+$19,230/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="I6" s="24" t="inlineStr">
+        <is>
+          <t>H | 493呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 440呎 (2房)
+$909万
+$20,655/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 447呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>D | 245呎 (开放式)
+$482万
+$19,694/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>E | 246呎 (开放式)
+$464万
+$18,866/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>F | 246呎 (开放式)
+$467万
+$18,980/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>G | 300呎 (1房)
+$571万
+$19,043/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="I7" s="21" t="inlineStr">
+        <is>
+          <t>H | 493呎 (2房)
+$1196万
+$24,256/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 440呎 (2房)
+$889万
+$20,214/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 447呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>C | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>D | 245呎 (开放式)
+$478万
+$19,498/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>E | 246呎 (开放式)
+$454万
+$18,476/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>F | 246呎 (开放式)
+$462万
+$18,793/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>G | 300呎 (1房)
+$566万
+$18,853/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="I8" s="21" t="inlineStr">
+        <is>
+          <t>H | 493呎 (2房)
+$1184万
+$24,016/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 440呎 (2房)
+$881万
+$20,014/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 447呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>C | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 245呎 (开放式)
+$468万
+$19,098/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>E | 246呎 (开放式)
+$450万
+$18,293/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>F | 246呎 (开放式)
+$458万
+$18,602/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>G | 300呎 (1房)
+$560万
+$18,667/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="I9" s="21" t="inlineStr">
+        <is>
+          <t>H | 493呎 (2房)
+$1172万
+$23,779/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 440呎 (2房)
+$886万
+$20,148/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 447呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>C | 311呎 (1房)
+$743万
+$23,878/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>D | 245呎 (开放式)
+$460万
+$18,792/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>E | 246呎 (开放式)
+$448万
+$18,207/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>F | 246呎 (开放式)
+$450万
+$18,305/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>G | 300呎 (1房)
+$557万
+$18,570/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
+        <is>
+          <t>H | 493呎 (2房)
+$1059万
+$21,473/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 440呎 (2房)
+$882万
+$20,048/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 447呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>C | 311呎 (1房)
+$739万
+$23,759/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>D | 245呎 (开放式)
+$458万
+$18,698/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>E | 247呎 (开放式)
+$446万
+$18,036/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="inlineStr">
+        <is>
+          <t>F | 246呎 (开放式)
+$448万
+$18,220/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="inlineStr">
+        <is>
+          <t>G | 300呎 (1房)
+$554万
+$18,480/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="I11" s="20" t="inlineStr">
+        <is>
+          <t>H | 493呎 (2房)
+$1030万
+$20,895/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 440呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 447呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>C | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>D | 245呎 (开放式)
+$506万
+$20,669/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t>E | 247呎 (开放式)
+$492万
+$19,939/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G12" s="21" t="inlineStr">
+        <is>
+          <t>F | 247呎 (开放式)
+$495万
+$20,053/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t>G | 300呎 (1房)
+$613万
+$20,427/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I12" s="21" t="inlineStr">
+        <is>
+          <t>H | 493呎 (2房)
+$1155万
+$23,424/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 440呎 (2房)
+$863万
+$19,616/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 447呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>C | 311呎 (1房)
+$732万
+$23,521/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>D | 245呎 (开放式)
+$466万
+$19,029/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>E | 247呎 (开放式)
+$441万
+$17,862/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="inlineStr">
+        <is>
+          <t>F | 246呎 (开放式)
+$444万
+$18,037/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H13" s="20" t="inlineStr">
+        <is>
+          <t>G | 300呎 (1房)
+$549万
+$18,300/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="I13" s="20" t="inlineStr">
+        <is>
+          <t>H | 493呎 (2房)
+$1020万
+$20,688/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 440呎 (2房)
+$859万
+$19,520/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 447呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>C | 311呎 (1房)
+$728万
+$23,405/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>D | 245呎 (开放式)
+$464万
+$18,931/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>E | 246呎 (开放式)
+$439万
+$17,846/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>F | 246呎 (开放式)
+$442万
+$17,947/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H14" s="20" t="inlineStr">
+        <is>
+          <t>G | 300呎 (1房)
+$546万
+$18,207/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="I14" s="20" t="inlineStr">
+        <is>
+          <t>H | 493呎 (2房)
+$1015万
+$20,584/呎
+(25年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 440呎 (2房)
+$855万
+$19,423/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 447呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>C | 311呎 (1房)
+$724万
+$23,289/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>D | 245呎 (开放式)
+$462万
+$18,841/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>E | 247呎 (开放式)
+$437万
+$17,684/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G15" s="20" t="inlineStr">
+        <is>
+          <t>F | 246呎 (开放式)
+$444万
+$18,053/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H15" s="20" t="inlineStr">
+        <is>
+          <t>G | 300呎 (1房)
+$544万
+$18,117/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="I15" s="20" t="inlineStr">
+        <is>
+          <t>H | 493呎 (2房)
+$1010万
+$20,483/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 440呎 (2房)
+$850万
+$19,327/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 447呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>C | 311呎 (1房)
+$721万
+$23,174/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>D | 245呎 (开放式)
+$447万
+$18,237/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>E | 246呎 (开放式)
+$435万
+$17,671/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
+        <is>
+          <t>F | 246呎 (开放式)
+$437万
+$17,768/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="H16" s="20" t="inlineStr">
+        <is>
+          <t>G | 300呎 (1房)
+$541万
+$18,027/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="I16" s="20" t="inlineStr">
+        <is>
+          <t>H | 493呎 (2房)
+$1005万
+$20,379/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 440呎 (2房)
+$846万
+$19,230/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 447呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>C | 311呎 (1房)
+$717万
+$23,058/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>D | 245呎 (开放式)
+$445万
+$18,147/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>E | 247呎 (开放式)
+$432万
+$17,510/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="inlineStr">
+        <is>
+          <t>F | 246呎 (开放式)
+$435万
+$17,679/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>G | 300呎 (1房)
+$538万
+$17,937/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="I17" s="20" t="inlineStr">
+        <is>
+          <t>H | 493呎 (2房)
+$1000万
+$20,278/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 440呎 (2房)
+$822万
+$18,684/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 447呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>C | 311呎 (1房)
+$714万
+$22,942/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>D | 245呎 (开放式)
+$457万
+$18,657/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>E | 247呎 (开放式)
+$430万
+$17,417/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="G18" s="20" t="inlineStr">
+        <is>
+          <t>F | 246呎 (开放式)
+$433万
+$17,593/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H18" s="20" t="inlineStr">
+        <is>
+          <t>G | 300呎 (1房)
+$535万
+$17,847/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="I18" s="20" t="inlineStr">
+        <is>
+          <t>H | 493呎 (2房)
+$1006万
+$20,404/呎
+(25年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 440呎 (2房)
+$818万
+$18,589/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 447呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>C | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>D | 245呎 (开放式)
+$455万
+$18,563/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>E | 246呎 (开放式)
+$428万
+$17,402/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G19" s="20" t="inlineStr">
+        <is>
+          <t>F | 246呎 (开放式)
+$431万
+$17,504/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H19" s="20" t="inlineStr">
+        <is>
+          <t>G | 300呎 (1房)
+$533万
+$17,757/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="I19" s="20" t="inlineStr">
+        <is>
+          <t>H | 493呎 (2房)
+$990万
+$20,075/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 440呎 (2房)
+$814万
+$18,498/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 447呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>D | 245呎 (开放式)
+$453万
+$18,473/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>E | 246呎 (开放式)
+$426万
+$17,317/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G20" s="20" t="inlineStr">
+        <is>
+          <t>F | 246呎 (开放式)
+$428万
+$17,415/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H20" s="20" t="inlineStr">
+        <is>
+          <t>G | 300呎 (1房)
+$530万
+$17,667/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="I20" s="20" t="inlineStr">
+        <is>
+          <t>H | 493呎 (2房)
+$985万
+$19,976/呎
+(25年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 440呎 (2房)
+$810万
+$18,405/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 447呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>D | 245呎 (开放式)
+$450万
+$18,380/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>E | 247呎 (开放式)
+$424万
+$17,162/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G21" s="20" t="inlineStr">
+        <is>
+          <t>F | 246呎 (开放式)
+$426万
+$17,329/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="H21" s="20" t="inlineStr">
+        <is>
+          <t>G | 300呎 (1房)
+$527万
+$17,580/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="I21" s="20" t="inlineStr">
+        <is>
+          <t>H | 493呎 (2房)
+$980万
+$19,874/呎
+(25年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 440呎 (2房)
+$809万
+$18,384/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 447呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>D | 245呎 (开放式)
+$442万
+$18,057/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>E | 247呎 (开放式)
+$421万
+$17,040/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="G22" s="20" t="inlineStr">
+        <is>
+          <t>F | 246呎 (开放式)
+$423万
+$17,207/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H22" s="20" t="inlineStr">
+        <is>
+          <t>G | 300呎 (1房)
+$524万
+$17,457/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="I22" s="21" t="inlineStr">
+        <is>
+          <t>H | 493呎 (2房)
+$1096万
+$22,237/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 440呎 (2房)
+$808万
+$18,359/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 447呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>C | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>D | 245呎 (开放式)
+$439万
+$17,931/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>E | 247呎 (开放式)
+$418万
+$16,919/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="G23" s="20" t="inlineStr">
+        <is>
+          <t>F | 246呎 (开放式)
+$420万
+$17,085/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H23" s="20" t="inlineStr">
+        <is>
+          <t>G | 300呎 (1房)
+$520万
+$17,333/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="I23" s="21" t="inlineStr">
+        <is>
+          <t>H | 493呎 (2房)
+$1087万
+$22,049/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 440呎 (2房)
+$800万
+$18,177/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 447呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D24" s="25" t="inlineStr"/>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>D | 251呎 (开放式)
+$491万
+$19,546/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F24" s="20" t="inlineStr">
+        <is>
+          <t>E | 247呎 (开放式)
+$415万
+$16,798/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="G24" s="20" t="inlineStr">
+        <is>
+          <t>F | 246呎 (开放式)
+$417万
+$16,967/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H24" s="20" t="inlineStr">
+        <is>
+          <t>G | 300呎 (1房)
+$516万
+$17,213/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="I24" s="24" t="inlineStr">
+        <is>
+          <t>H | 493呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>A | 440呎 (2房)
+$785万
+$17,845/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>B | 447呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D25" s="25" t="inlineStr"/>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>D | 251呎 (开放式)
+$438万
+$17,438/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
+        <is>
+          <t>E | 247呎 (开放式)
+$412万
+$16,684/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="G25" s="20" t="inlineStr">
+        <is>
+          <t>F | 246呎 (开放式)
+$414万
+$16,850/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
+        <is>
+          <t>G | 300呎 (1房)
+$513万
+$17,093/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="I25" s="20" t="inlineStr">
+        <is>
+          <t>H | 493呎 (2房)
+$955万
+$19,363/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>A | 440呎 (2房)
+$774万
+$17,584/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>B | 447呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D26" s="25" t="inlineStr"/>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>D | 251呎 (开放式)
+$435万
+$17,315/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F26" s="20" t="inlineStr">
+        <is>
+          <t>E | 247呎 (开放式)
+$412万
+$16,660/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G26" s="20" t="inlineStr">
+        <is>
+          <t>F | 246呎 (开放式)
+$414万
+$16,821/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H26" s="20" t="inlineStr">
+        <is>
+          <t>G | 300呎 (1房)
+$509万
+$16,973/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="I26" s="21" t="inlineStr">
+        <is>
+          <t>H | 493呎 (2房)
+$1049万
+$21,282/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>A | 440呎 (2房)
+$761万
+$17,295/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>B | 447呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D27" s="25" t="inlineStr"/>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>D | 251呎 (开放式)
+$432万
+$17,195/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="inlineStr">
+        <is>
+          <t>E | 247呎 (开放式)
+$409万
+$16,547/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G27" s="20" t="inlineStr">
+        <is>
+          <t>F | 246呎 (开放式)
+$411万
+$16,703/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="H27" s="20" t="inlineStr">
+        <is>
+          <t>G | 300呎 (1房)
+$506万
+$16,853/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="I27" s="21" t="inlineStr">
+        <is>
+          <t>H | 493呎 (2房)
+$1036万
+$21,012/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>A | 440呎 (2房)
+$747万
+$16,975/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>B | 447呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D28" s="25" t="inlineStr"/>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>D | 251呎 (开放式)
+$477万
+$19,008/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F28" s="20" t="inlineStr">
+        <is>
+          <t>E | 247呎 (开放式)
+$408万
+$16,514/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G28" s="20" t="inlineStr">
+        <is>
+          <t>F | 246呎 (开放式)
+$410万
+$16,683/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H28" s="20" t="inlineStr">
+        <is>
+          <t>G | 300呎 (1房)
+$502万
+$16,737/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="I28" s="24" t="inlineStr">
+        <is>
+          <t>H | 493呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2A座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>A | 440呎 (2房)
+$1267万
+$28,805/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C5" s="22" t="inlineStr">
+        <is>
+          <t>B | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>C | 244呎 (开放式)
+$580万
+$23,758/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+$654万
+$21,439/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F5" s="22" t="inlineStr">
+        <is>
+          <t>E | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G5" s="22" t="inlineStr">
+        <is>
+          <t>F | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H5" s="21" t="inlineStr">
+        <is>
+          <t>G | 494呎 (2房)
+$1482万
+$29,990/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 440呎 (2房)
+$1255万
+$28,520/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 244呎 (开放式)
+$574万
+$23,525/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+$648万
+$21,230/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>E | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t>F | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t>G | 494呎 (2房)
+$1467万
+$29,694/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A | 440呎 (2房)
+$1242万
+$28,239/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="24" t="inlineStr">
+        <is>
+          <t>C | 244呎 (开放式)
+$644万
+$26,393/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+$641万
+$21,016/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>E | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G7" s="22" t="inlineStr">
+        <is>
+          <t>F | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t>G | 494呎 (2房)
+$1452万
+$29,401/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 440呎 (2房)
+$1230万
+$27,959/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>C | 244呎 (开放式)
+$574万
+$23,525/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+$621万
+$20,357/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>E | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G8" s="22" t="inlineStr">
+        <is>
+          <t>F | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t>G | 494呎 (2房)
+$1438万
+$29,109/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 439呎 (2房)
+$1096万
+$24,970/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 244呎 (开放式)
+$557万
+$22,836/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+$615万
+$20,154/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>E | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t>F | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H9" s="24" t="inlineStr">
+        <is>
+          <t>G | 494呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 440呎 (2房)
+$1319万
+$29,982/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 244呎 (开放式)
+$552万
+$22,611/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+$609万
+$19,954/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>E | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="inlineStr">
+        <is>
+          <t>F | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H10" s="24" t="inlineStr">
+        <is>
+          <t>G | 494呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 439呎 (2房)
+$1274万
+$29,027/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 244呎 (开放式)
+$543万
+$22,270/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+$606万
+$19,856/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>E | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="inlineStr">
+        <is>
+          <t>F | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="inlineStr">
+        <is>
+          <t>G | 494呎 (2房)
+$1301万
+$26,342/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 439呎 (2房)
+$1075万
+$24,478/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 244呎 (开放式)
+$547万
+$22,406/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+$603万
+$19,757/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>E | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t>F | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H12" s="24" t="inlineStr">
+        <is>
+          <t>G | 494呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>A | 440呎 (2房)
+$1188万
+$27,000/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>C | 244呎 (开放式)
+$543万
+$22,270/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+$666万
+$21,843/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>E | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="inlineStr">
+        <is>
+          <t>F | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t>G | 494呎 (2房)
+$1389万
+$28,111/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>A | 440呎 (2房)
+$1182万
+$26,866/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 244呎 (开放式)
+$541万
+$22,164/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+$597万
+$19,564/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>E | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>F | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H14" s="21" t="inlineStr">
+        <is>
+          <t>G | 494呎 (2房)
+$1382万
+$27,972/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>A | 440呎 (2房)
+$1176万
+$26,732/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>C | 244呎 (开放式)
+$550万
+$22,541/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+$594万
+$19,466/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>E | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>F | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H15" s="21" t="inlineStr">
+        <is>
+          <t>G | 494呎 (2房)
+$1375万
+$27,832/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>A | 440呎 (2房)
+$1170万
+$26,600/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>C | 244呎 (开放式)
+$542万
+$22,201/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+$591万
+$19,367/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>E | 305呎 (1房)
+$604万
+$19,797/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G16" s="22" t="inlineStr">
+        <is>
+          <t>F | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H16" s="21" t="inlineStr">
+        <is>
+          <t>G | 494呎 (2房)
+$1368万
+$27,694/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>A | 440呎 (2房)
+$1165万
+$26,468/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 244呎 (开放式)
+$527万
+$21,615/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+$588万
+$19,269/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>E | 305呎 (1房)
+$614万
+$20,128/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G17" s="22" t="inlineStr">
+        <is>
+          <t>F | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H17" s="21" t="inlineStr">
+        <is>
+          <t>G | 494呎 (2房)
+$1361万
+$27,557/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 439呎 (2房)
+$1043万
+$23,756/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>C | 244呎 (开放式)
+$530万
+$21,721/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+$585万
+$19,177/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>E | 305呎 (1房)
+$598万
+$19,600/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
+        <is>
+          <t>F | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H18" s="20" t="inlineStr">
+        <is>
+          <t>G | 494呎 (2房)
+$1219万
+$24,678/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 440呎 (2房)
+$1038万
+$23,584/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>C | 244呎 (开放式)
+$527万
+$21,611/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+$582万
+$19,079/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>E | 305呎 (1房)
+$595万
+$19,502/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G19" s="22" t="inlineStr">
+        <is>
+          <t>F | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H19" s="20" t="inlineStr">
+        <is>
+          <t>G | 494呎 (2房)
+$1213万
+$24,555/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 439呎 (2房)
+$1032万
+$23,519/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>C | 244呎 (开放式)
+$525万
+$21,504/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+$579万
+$18,984/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>E | 305呎 (1房)
+$645万
+$21,151/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G20" s="22" t="inlineStr">
+        <is>
+          <t>F | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H20" s="20" t="inlineStr">
+        <is>
+          <t>G | 494呎 (2房)
+$1387万
+$28,079/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 439呎 (2房)
+$1027万
+$23,401/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>C | 244呎 (开放式)
+$525万
+$21,504/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+$582万
+$19,098/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>E | 305呎 (1房)
+$589万
+$19,305/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G21" s="22" t="inlineStr">
+        <is>
+          <t>F | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H21" s="20" t="inlineStr">
+        <is>
+          <t>G | 494呎 (2房)
+$1380万
+$27,941/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 440呎 (2房)
+$1022万
+$23,232/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>C | 244呎 (开放式)
+$522万
+$21,402/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+$573万
+$18,797/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>E | 305呎 (1房)
+$599万
+$19,626/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G22" s="22" t="inlineStr">
+        <is>
+          <t>F | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H22" s="20" t="inlineStr">
+        <is>
+          <t>G | 494呎 (2房)
+$1195万
+$24,188/呎
+(25年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>A | 440呎 (2房)
+$1128万
+$25,632/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>C | 244呎 (开放式)
+$516万
+$21,148/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+$569万
+$18,662/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>E | 305呎 (1房)
+$594万
+$19,492/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G23" s="22" t="inlineStr">
+        <is>
+          <t>F | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H23" s="21" t="inlineStr">
+        <is>
+          <t>G | 494呎 (2房)
+$1318万
+$26,686/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>A | 440呎 (2房)
+$1120万
+$25,452/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>C | 244呎 (开放式)
+$509万
+$20,869/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+$563万
+$18,459/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="F24" s="20" t="inlineStr">
+        <is>
+          <t>E | 305呎 (1房)
+$577万
+$18,905/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G24" s="22" t="inlineStr">
+        <is>
+          <t>F | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H24" s="21" t="inlineStr">
+        <is>
+          <t>G | 494呎 (2房)
+$1309万
+$26,500/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>A | 440呎 (2房)
+$1112万
+$25,273/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>B | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>C | 244呎 (开放式)
+$499万
+$20,467/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+$554万
+$18,148/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
+        <is>
+          <t>E | 305呎 (1房)
+$582万
+$19,066/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G25" s="22" t="inlineStr">
+        <is>
+          <t>F | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H25" s="21" t="inlineStr">
+        <is>
+          <t>G | 494呎 (2房)
+$1300万
+$26,314/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>A | 439呎 (2房)
+$1173万
+$26,715/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>B | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>C | 244呎 (开放式)
+$496万
+$20,340/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+$546万
+$17,911/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F26" s="20" t="inlineStr">
+        <is>
+          <t>E | 305呎 (1房)
+$576万
+$18,869/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G26" s="22" t="inlineStr">
+        <is>
+          <t>F | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H26" s="20" t="inlineStr">
+        <is>
+          <t>G | 494呎 (2房)
+$1162万
+$23,518/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t>A | 440呎 (2房)
+$1096万
+$24,920/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>B | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D27" s="21" t="inlineStr">
+        <is>
+          <t>C | 244呎 (开放式)
+$486万
+$19,918/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+$540万
+$17,715/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="inlineStr">
+        <is>
+          <t>E | 305呎 (1房)
+$559万
+$18,325/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G27" s="22" t="inlineStr">
+        <is>
+          <t>F | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H27" s="21" t="inlineStr">
+        <is>
+          <t>G | 494呎 (2房)
+$1282万
+$25,947/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B28" s="21" t="inlineStr">
+        <is>
+          <t>A | 440呎 (2房)
+$1089万
+$24,748/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>B | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D28" s="21" t="inlineStr">
+        <is>
+          <t>C | 244呎 (开放式)
+$480万
+$19,660/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+$534万
+$17,521/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F28" s="20" t="inlineStr">
+        <is>
+          <t>E | 305呎 (1房)
+$577万
+$18,931/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G28" s="22" t="inlineStr">
+        <is>
+          <t>F | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H28" s="21" t="inlineStr">
+        <is>
+          <t>G | 494呎 (2房)
+$1273万
+$25,765/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B29" s="21" t="inlineStr">
+        <is>
+          <t>A | 440呎 (2房)
+$1081万
+$24,573/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="inlineStr">
+        <is>
+          <t>B | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D29" s="21" t="inlineStr">
+        <is>
+          <t>C | 244呎 (开放式)
+$470万
+$19,250/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+$524万
+$17,174/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F29" s="20" t="inlineStr">
+        <is>
+          <t>E | 305呎 (1房)
+$570万
+$18,685/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G29" s="22" t="inlineStr">
+        <is>
+          <t>F | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H29" s="21" t="inlineStr">
+        <is>
+          <t>G | 494呎 (2房)
+$1264万
+$25,585/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2B座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 593呎 (3房)
+$1658万
+$27,966/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 306呎 (1房)
+$662万
+$21,631/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 447呎 (2房)
+$1010万
+$22,591/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 1770呎 (4+房)
+$7080万
+$40,000/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="F5" s="25" t="inlineStr"/>
+      <c r="G5" s="25" t="inlineStr"/>
+      <c r="H5" s="25" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 593呎 (3房)
+$1824万
+$30,762/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 306呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>C | 445呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>D | 447呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>E | 496呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>F | 705呎 (3房)
+$2261万
+$32,065/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>G | 657呎 (3房)
+$1854万
+$28,221/呎
+(25年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A | 593呎 (3房)
+$1806万
+$30,459/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 306呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 445呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>D | 447呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>E | 496呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G7" s="21" t="inlineStr">
+        <is>
+          <t>F | 705呎 (3房)
+$2238万
+$31,748/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t>G | 657呎 (3房)
+$2040万
+$31,046/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 593呎 (3房)
+$1788万
+$30,157/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 306呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>C | 445呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>D | 447呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>E | 496呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G8" s="21" t="inlineStr">
+        <is>
+          <t>F | 705呎 (3房)
+$2216万
+$31,434/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t>G | 657呎 (3房)
+$2020万
+$30,738/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>A | 593呎 (3房)
+$1771万
+$29,858/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 306呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>C | 445呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>D | 447呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>E | 496呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>F | 705呎 (3房)
+$2185万
+$30,987/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>G | 657呎 (3房)
+$2000万
+$30,434/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>A | 593呎 (3房)
+$1753万
+$29,563/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 306呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>C | 445呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="inlineStr">
+        <is>
+          <t>D | 447呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>E | 496呎 (2房)
+$1480万
+$29,829/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>F | 705呎 (3房)
+$2207万
+$31,308/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t>G | 657呎 (3房)
+$1980万
+$30,132/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>A | 593呎 (3房)
+$1744万
+$29,415/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 306呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>C | 445呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>D | 447呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>E | 496呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="inlineStr">
+        <is>
+          <t>F | 705呎 (3房)
+$1946万
+$27,596/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t>G | 657呎 (3房)
+$1970万
+$29,982/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>A | 593呎 (3房)
+$1736万
+$29,270/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 306呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>C | 445呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="inlineStr">
+        <is>
+          <t>D | 447呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>E | 496呎 (2房)
+$1366万
+$27,546/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="inlineStr">
+        <is>
+          <t>F | 705呎 (3房)
+$1936万
+$27,460/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t>G | 657呎 (3房)
+$1960万
+$29,833/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>A | 593呎 (3房)
+$1727万
+$29,123/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 306呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 445呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>D | 447呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>E | 496呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G13" s="21" t="inlineStr">
+        <is>
+          <t>F | 705呎 (3房)
+$2140万
+$30,357/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t>G | 657呎 (3房)
+$1950万
+$29,685/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>A | 593呎 (3房)
+$1718万
+$28,978/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 306呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 445呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>D | 447呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>E | 496呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G14" s="21" t="inlineStr">
+        <is>
+          <t>F | 705呎 (3房)
+$2130万
+$30,206/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H14" s="21" t="inlineStr">
+        <is>
+          <t>G | 657呎 (3房)
+$1941万
+$29,537/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>A | 593呎 (3房)
+$1710万
+$28,835/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 306呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 445呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>D | 447呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>E | 496呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G15" s="20" t="inlineStr">
+        <is>
+          <t>F | 705呎 (3房)
+$2153万
+$30,538/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H15" s="20" t="inlineStr">
+        <is>
+          <t>G | 658呎 (3房)
+$2060万
+$31,301/呎
+(26年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>A | 593呎 (3房)
+$1701万
+$28,691/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 306呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>C | 445呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>D | 447呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>E | 496呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G16" s="21" t="inlineStr">
+        <is>
+          <t>F | 705呎 (3房)
+$2108万
+$29,906/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H16" s="21" t="inlineStr">
+        <is>
+          <t>G | 657呎 (3房)
+$1921万
+$29,244/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>A | 593呎 (3房)
+$1693万
+$28,548/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 306呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>C | 445呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E17" s="24" t="inlineStr">
+        <is>
+          <t>D | 447呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F17" s="24" t="inlineStr">
+        <is>
+          <t>E | 496呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="inlineStr">
+        <is>
+          <t>F | 705呎 (3房)
+$2192万
+$31,085/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>G | 658呎 (3房)
+$1995万
+$30,322/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>A | 593呎 (3房)
+$1684万
+$28,405/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 306呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>C | 445呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E18" s="24" t="inlineStr">
+        <is>
+          <t>D | 447呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>E | 496呎 (2房)
+$1326万
+$26,736/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G18" s="20" t="inlineStr">
+        <is>
+          <t>F | 705呎 (3房)
+$1879万
+$26,648/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="H18" s="20" t="inlineStr">
+        <is>
+          <t>G | 658呎 (3房)
+$1933万
+$29,372/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>A | 593呎 (3房)
+$1676万
+$28,263/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 306呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>C | 445呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>D | 447呎 (2房)
+$1099万
+$24,586/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F19" s="24" t="inlineStr">
+        <is>
+          <t>E | 496呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="G19" s="20" t="inlineStr">
+        <is>
+          <t>F | 705呎 (3房)
+$2110万
+$29,933/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H19" s="21" t="inlineStr">
+        <is>
+          <t>G | 657呎 (3房)
+$1893万
+$28,808/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>A | 593呎 (3房)
+$1668万
+$28,121/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 306呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 445呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>D | 447呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>E | 496呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G20" s="20" t="inlineStr">
+        <is>
+          <t>F | 705呎 (3房)
+$1860万
+$26,383/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H20" s="21" t="inlineStr">
+        <is>
+          <t>G | 657呎 (3房)
+$1883万
+$28,664/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>A | 593呎 (3房)
+$1659万
+$27,981/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 306呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 445呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>D | 447呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
+        <is>
+          <t>E | 496呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G21" s="20" t="inlineStr">
+        <is>
+          <t>F | 705呎 (3房)
+$1892万
+$26,834/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H21" s="20" t="inlineStr">
+        <is>
+          <t>G | 658呎 (3房)
+$1904万
+$28,935/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>A | 593呎 (3房)
+$1651万
+$27,841/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 306呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 445呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>D | 447呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
+        <is>
+          <t>E | 496呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G22" s="20" t="inlineStr">
+        <is>
+          <t>F | 705呎 (3房)
+$1841万
+$26,119/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H22" s="20" t="inlineStr">
+        <is>
+          <t>G | 658呎 (3房)
+$1678万
+$25,503/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>A | 593呎 (3房)
+$1639万
+$27,646/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 306呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>C | 445呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>D | 447呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
+        <is>
+          <t>E | 496呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G23" s="21" t="inlineStr">
+        <is>
+          <t>F | 705呎 (3房)
+$2032万
+$28,817/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H23" s="21" t="inlineStr">
+        <is>
+          <t>G | 657呎 (3房)
+$1851万
+$28,180/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>A | 593呎 (3房)
+$1628万
+$27,454/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 306呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>C | 445呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>D | 447呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
+        <is>
+          <t>E | 496呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
+        <is>
+          <t>F | 705呎 (3房)
+$2017万
+$28,616/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H24" s="21" t="inlineStr">
+        <is>
+          <t>G | 657呎 (3房)
+$1838万
+$27,983/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>A | 593呎 (3房)
+$1617万
+$27,261/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>B | 306呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>C | 445呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>D | 447呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F25" s="22" t="inlineStr">
+        <is>
+          <t>E | 496呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G25" s="21" t="inlineStr">
+        <is>
+          <t>F | 705呎 (3房)
+$2003万
+$28,416/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H25" s="21" t="inlineStr">
+        <is>
+          <t>G | 657呎 (3房)
+$1826万
+$27,787/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
+        <is>
+          <t>A | 593呎 (3房)
+$1605万
+$27,071/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>B | 306呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>C | 445呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>D | 447呎 (2房)
+$1053万
+$23,548/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F26" s="24" t="inlineStr">
+        <is>
+          <t>E | 496呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="G26" s="20" t="inlineStr">
+        <is>
+          <t>F | 705呎 (3房)
+$2122万
+$30,104/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H26" s="24" t="inlineStr">
+        <is>
+          <t>G | 657呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t>A | 593呎 (3房)
+$1594万
+$26,880/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>B | 306呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>C | 445呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>D | 447呎 (2房)
+$1042万
+$23,300/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F27" s="24" t="inlineStr">
+        <is>
+          <t>E | 496呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="G27" s="21" t="inlineStr">
+        <is>
+          <t>F | 705呎 (3房)
+$1975万
+$28,020/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H27" s="21" t="inlineStr">
+        <is>
+          <t>G | 657呎 (3房)
+$1800万
+$27,399/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B28" s="21" t="inlineStr">
+        <is>
+          <t>A | 593呎 (3房)
+$1583万
+$26,693/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>B | 306呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>C | 445呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>D | 447呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F28" s="22" t="inlineStr">
+        <is>
+          <t>E | 496呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G28" s="21" t="inlineStr">
+        <is>
+          <t>F | 705呎 (3房)
+$1962万
+$27,823/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H28" s="21" t="inlineStr">
+        <is>
+          <t>G | 657呎 (3房)
+$1788万
+$27,207/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B29" s="21" t="inlineStr">
+        <is>
+          <t>A | 593呎 (3房)
+$1572万
+$26,506/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="inlineStr">
+        <is>
+          <t>B | 306呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="inlineStr">
+        <is>
+          <t>C | 445呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="inlineStr">
+        <is>
+          <t>D | 447呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F29" s="22" t="inlineStr">
+        <is>
+          <t>E | 496呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G29" s="21" t="inlineStr">
+        <is>
+          <t>F | 705呎 (3房)
+$1948万
+$27,628/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H29" s="21" t="inlineStr">
+        <is>
+          <t>G | 657呎 (3房)
+$1775万
+$27,017/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-启德-维港．双钻.xlsx
+++ b/files/九龙-启德-维港．双钻.xlsx
@@ -673,7 +673,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/九龙-启德-维港．双钻.xlsx
+++ b/files/九龙-启德-维港．双钻.xlsx
@@ -46037,7 +46037,7 @@
           <t>A | 493呎 (2房)
 $1040万
 $21,089/呎
-(25年-07月)</t>
+(25年-07月-13日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -46045,7 +46045,7 @@
           <t>B | 305呎 (1房)
 $589万
 $19,311/呎
-(25年-07月)</t>
+(25年-07月-07日)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -46053,7 +46053,7 @@
           <t>C | 305呎 (1房)
 $596万
 $19,525/呎
-(25年-07月)</t>
+(25年-07月-31日)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -46061,7 +46061,7 @@
           <t>D | 305呎 (1房)
 $638万
 $20,925/呎
-(26年-03月)</t>
+(26年-03月-11日)</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
@@ -46069,7 +46069,7 @@
           <t>E | 301呎 (1房)
 $638万
 $21,196/呎
-(25年-07月)</t>
+(25年-07月-13日)</t>
         </is>
       </c>
       <c r="G5" s="21" t="inlineStr">
@@ -46085,7 +46085,7 @@
           <t>G | 437呎 (2房)
 $883万
 $20,208/呎
-(25年-11月)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
     </row>
@@ -46100,7 +46100,7 @@
           <t>A | 493呎 (2房)
 $1018万
 $20,643/呎
-(25年-07月)</t>
+(25年-07月-07日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -46108,7 +46108,7 @@
           <t>B | 305呎 (1房)
 $583万
 $19,121/呎
-(25年-06月)</t>
+(25年-06月-29日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -46116,7 +46116,7 @@
           <t>C | 305呎 (1房)
 $590万
 $19,328/呎
-(25年-06月)</t>
+(25年-06月-24日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -46124,7 +46124,7 @@
           <t>D | 305呎 (1房)
 $596万
 $19,541/呎
-(25年-06月)</t>
+(25年-06月-08日)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -46132,7 +46132,7 @@
           <t>E | 301呎 (1房)
 $625万
 $20,754/呎
-(25年-07月)</t>
+(25年-07月-29日)</t>
         </is>
       </c>
       <c r="G6" s="21" t="inlineStr">
@@ -46148,7 +46148,7 @@
           <t>G | 437呎 (2房)
 $874万
 $20,007/呎
-(25年-11月)</t>
+(25年-11月-30日)</t>
         </is>
       </c>
     </row>
@@ -46163,7 +46163,7 @@
           <t>A | 493呎 (2房)
 $1008万
 $20,440/呎
-(25年-06月)</t>
+(25年-06月-25日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -46171,7 +46171,7 @@
           <t>B | 305呎 (1房)
 $577万
 $18,931/呎
-(25年-06月)</t>
+(25年-06月-19日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -46179,7 +46179,7 @@
           <t>C | 305呎 (1房)
 $584万
 $19,138/呎
-(25年-06月)</t>
+(25年-06月-24日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -46187,7 +46187,7 @@
           <t>D | 305呎 (1房)
 $590万
 $19,348/呎
-(25年-06月)</t>
+(25年-06月-10日)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -46195,7 +46195,7 @@
           <t>E | 301呎 (1房)
 $619万
 $20,551/呎
-(25年-07月)</t>
+(25年-07月-20日)</t>
         </is>
       </c>
       <c r="G7" s="21" t="inlineStr">
@@ -46211,7 +46211,7 @@
           <t>G | 437呎 (2房)
 $866万
 $19,810/呎
-(25年-10月)</t>
+(25年-10月-27日)</t>
         </is>
       </c>
     </row>
@@ -46226,7 +46226,7 @@
           <t>A | 493呎 (2房)
 $998万
 $20,237/呎
-(25年-07月)</t>
+(25年-07月-07日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -46234,7 +46234,7 @@
           <t>B | 305呎 (1房)
 $578万
 $18,954/呎
-(25年-06月)</t>
+(25年-06月-09日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -46242,7 +46242,7 @@
           <t>C | 305呎 (1房)
 $578万
 $18,951/呎
-(25年-06月)</t>
+(25年-06月-09日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -46250,7 +46250,7 @@
           <t>D | 305呎 (1房)
 $584万
 $19,154/呎
-(25年-05月)</t>
+(25年-05月-25日)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -46258,7 +46258,7 @@
           <t>E | 301呎 (1房)
 $610万
 $20,249/呎
-(25年-07月)</t>
+(25年-07月-20日)</t>
         </is>
       </c>
       <c r="G8" s="21" t="inlineStr">
@@ -46274,7 +46274,7 @@
           <t>G | 437呎 (2房)
 $867万
 $19,844/呎
-(25年-10月)</t>
+(25年-10月-12日)</t>
         </is>
       </c>
     </row>
@@ -46289,7 +46289,7 @@
           <t>A | 493呎 (2房)
 $988万
 $20,034/呎
-(25年-07月)</t>
+(25年-07月-01日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -46297,7 +46297,7 @@
           <t>B | 305呎 (1房)
 $572万
 $18,764/呎
-(25年-06月)</t>
+(25年-06月-09日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -46305,7 +46305,7 @@
           <t>C | 305呎 (1房)
 $572万
 $18,761/呎
-(25年-05月)</t>
+(25年-05月-29日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -46313,7 +46313,7 @@
           <t>D | 305呎 (1房)
 $578万
 $18,967/呎
-(25年-05月)</t>
+(25年-05月-25日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -46321,7 +46321,7 @@
           <t>E | 301呎 (1房)
 $604万
 $20,050/呎
-(25年-07月)</t>
+(25年-07月-20日)</t>
         </is>
       </c>
       <c r="G9" s="21" t="inlineStr">
@@ -46337,7 +46337,7 @@
           <t>G | 437呎 (2房)
 $849万
 $19,421/呎
-(25年-09月)</t>
+(25年-09月-11日)</t>
         </is>
       </c>
     </row>
@@ -46352,7 +46352,7 @@
           <t>A | 493呎 (2房)
 $983万
 $19,935/呎
-(25年-06月)</t>
+(25年-06月-12日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -46360,7 +46360,7 @@
           <t>B | 305呎 (1房)
 $569万
 $18,669/呎
-(25年-06月)</t>
+(25年-06月-09日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -46368,7 +46368,7 @@
           <t>C | 305呎 (1房)
 $569万
 $18,669/呎
-(25年-05月)</t>
+(25年-05月-18日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -46376,7 +46376,7 @@
           <t>D | 305呎 (1房)
 $576万
 $18,872/呎
-(25年-05月)</t>
+(25年-05月-25日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -46384,7 +46384,7 @@
           <t>E | 301呎 (1房)
 $607万
 $20,169/呎
-(25年-06月)</t>
+(25年-06月-26日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -46392,7 +46392,7 @@
           <t>F | 447呎 (2房)
 $909万
 $20,338/呎
-(25年-11月)</t>
+(25年-11月-27日)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -46400,7 +46400,7 @@
           <t>G | 437呎 (2房)
 $844万
 $19,323/呎
-(25年-09月)</t>
+(25年-09月-04日)</t>
         </is>
       </c>
     </row>
@@ -46415,7 +46415,7 @@
           <t>A | 493呎 (2房)
 $978万
 $19,838/呎
-(25年-05月)</t>
+(25年-05月-21日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -46423,7 +46423,7 @@
           <t>B | 305呎 (1房)
 $567万
 $18,577/呎
-(25年-06月)</t>
+(25年-06月-09日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -46431,7 +46431,7 @@
           <t>C | 305呎 (1房)
 $567万
 $18,577/呎
-(25年-04月)</t>
+(25年-04月-09日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -46439,7 +46439,7 @@
           <t>D | 305呎 (1房)
 $573万
 $18,777/呎
-(25年-05月)</t>
+(25年-05月-27日)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -46447,7 +46447,7 @@
           <t>E | 301呎 (1房)
 $598万
 $19,854/呎
-(25年-07月)</t>
+(25年-07月-22日)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -46455,7 +46455,7 @@
           <t>F | 447呎 (2房)
 $905万
 $20,237/呎
-(25年-11月)</t>
+(25年-11月-27日)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -46463,7 +46463,7 @@
           <t>G | 437呎 (2房)
 $860万
 $19,682/呎
-(25年-08月)</t>
+(25年-08月-19日)</t>
         </is>
       </c>
     </row>
@@ -46541,7 +46541,7 @@
           <t>A | 493呎 (2房)
 $968万
 $19,641/呎
-(25年-05月)</t>
+(25年-05月-21日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -46549,7 +46549,7 @@
           <t>B | 305呎 (1房)
 $561万
 $18,393/呎
-(25年-06月)</t>
+(25年-06月-02日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -46557,7 +46557,7 @@
           <t>C | 305呎 (1房)
 $561万
 $18,390/呎
-(25年-04月)</t>
+(25年-04月-23日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -46565,7 +46565,7 @@
           <t>D | 305呎 (1房)
 $567万
 $18,590/呎
-(25年-05月)</t>
+(25年-05月-19日)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -46573,7 +46573,7 @@
           <t>E | 301呎 (1房)
 $592万
 $19,654/呎
-(25年-06月)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -46581,7 +46581,7 @@
           <t>F | 447呎 (2房)
 $896万
 $20,036/呎
-(25年-10月)</t>
+(25年-10月-12日)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -46589,7 +46589,7 @@
           <t>G | 437呎 (2房)
 $852万
 $19,485/呎
-(25年-09月)</t>
+(25年-09月-04日)</t>
         </is>
       </c>
     </row>
@@ -46604,7 +46604,7 @@
           <t>A | 493呎 (2房)
 $963万
 $19,542/呎
-(25年-05月)</t>
+(25年-05月-20日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -46612,7 +46612,7 @@
           <t>B | 305呎 (1房)
 $558万
 $18,302/呎
-(25年-05月)</t>
+(25年-05月-29日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -46620,7 +46620,7 @@
           <t>C | 305呎 (1房)
 $558万
 $18,298/呎
-(25年-04月)</t>
+(25年-04月-10日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -46628,7 +46628,7 @@
           <t>D | 305呎 (1房)
 $564万
 $18,502/呎
-(25年-05月)</t>
+(25年-05月-19日)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -46636,7 +46636,7 @@
           <t>E | 301呎 (1房)
 $614万
 $20,402/呎
-(26年-03月)</t>
+(26年-03月-11日)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -46644,7 +46644,7 @@
           <t>F | 447呎 (2房)
 $891万
 $19,935/呎
-(25年-09月)</t>
+(25年-09月-01日)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -46652,7 +46652,7 @@
           <t>G | 437呎 (2房)
 $828万
 $18,941/呎
-(25年-09月)</t>
+(25年-09月-03日)</t>
         </is>
       </c>
     </row>
@@ -46667,7 +46667,7 @@
           <t>A | 493呎 (2房)
 $959万
 $19,444/呎
-(25年-05月)</t>
+(25年-05月-20日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -46675,7 +46675,7 @@
           <t>B | 305呎 (1房)
 $568万
 $18,610/呎
-(25年-06月)</t>
+(25年-06月-03日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -46683,7 +46683,7 @@
           <t>C | 305呎 (1房)
 $555万
 $18,207/呎
-(25年-06月)</t>
+(25年-06月-05日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -46691,7 +46691,7 @@
           <t>D | 305呎 (1房)
 $561万
 $18,407/呎
-(25年-05月)</t>
+(25年-05月-19日)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -46699,7 +46699,7 @@
           <t>E | 301呎 (1房)
 $586万
 $19,458/呎
-(25年-06月)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -46707,7 +46707,7 @@
           <t>F | 447呎 (2房)
 $887万
 $19,837/呎
-(25年-10月)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -46715,7 +46715,7 @@
           <t>G | 437呎 (2房)
 $824万
 $18,849/呎
-(25年-10月)</t>
+(25年-10月-12日)</t>
         </is>
       </c>
     </row>
@@ -46730,7 +46730,7 @@
           <t>A | 493呎 (2房)
 $954万
 $19,349/呎
-(25年-04月)</t>
+(25年-04月-09日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -46738,7 +46738,7 @@
           <t>B | 305呎 (1房)
 $556万
 $18,216/呎
-(25年-06月)</t>
+(25年-06月-19日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -46746,7 +46746,7 @@
           <t>C | 305呎 (1房)
 $553万
 $18,118/呎
-(25年-05月)</t>
+(25年-05月-29日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -46754,7 +46754,7 @@
           <t>D | 305呎 (1房)
 $559万
 $18,315/呎
-(25年-05月)</t>
+(25年-05月-25日)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -46762,7 +46762,7 @@
           <t>E | 301呎 (1房)
 $583万
 $19,362/呎
-(25年-07月)</t>
+(25年-07月-01日)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -46770,7 +46770,7 @@
           <t>F | 447呎 (2房)
 $882万
 $19,738/呎
-(25年-10月)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -46778,7 +46778,7 @@
           <t>G | 437呎 (2房)
 $820万
 $18,753/呎
-(25年-07月)</t>
+(25年-07月-31日)</t>
         </is>
       </c>
     </row>
@@ -46793,7 +46793,7 @@
           <t>A | 493呎 (2房)
 $949万
 $19,252/呎
-(25年-02月)</t>
+(25年-02月-18日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -46801,7 +46801,7 @@
           <t>B | 305呎 (1房)
 $553万
 $18,128/呎
-(25年-06月)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -46809,7 +46809,7 @@
           <t>C | 305呎 (1房)
 $550万
 $18,030/呎
-(25年-04月)</t>
+(25年-04月-13日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -46817,7 +46817,7 @@
           <t>D | 305呎 (1房)
 $556万
 $18,223/呎
-(25年-04月)</t>
+(25年-04月-14日)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -46825,7 +46825,7 @@
           <t>E | 301呎 (1房)
 $577万
 $19,173/呎
-(25年-06月)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -46833,7 +46833,7 @@
           <t>F | 447呎 (2房)
 $878万
 $19,640/呎
-(25年-09月)</t>
+(25年-09月-10日)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -46841,7 +46841,7 @@
           <t>G | 437呎 (2房)
 $815万
 $18,659/呎
-(25年-07月)</t>
+(25年-07月-20日)</t>
         </is>
       </c>
     </row>
@@ -46856,7 +46856,7 @@
           <t>A | 493呎 (2房)
 $933万
 $18,933/呎
-(25年-01月)</t>
+(25年-01月-06日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -46864,7 +46864,7 @@
           <t>B | 305呎 (1房)
 $550万
 $18,036/呎
-(25年-06月)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -46872,7 +46872,7 @@
           <t>C | 305呎 (1房)
 $547万
 $17,938/呎
-(25年-04月)</t>
+(25年-04月-13日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -46880,7 +46880,7 @@
           <t>D | 305呎 (1房)
 $553万
 $18,131/呎
-(25年-04月)</t>
+(25年-04月-14日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -46888,7 +46888,7 @@
           <t>E | 301呎 (1房)
 $574万
 $19,073/呎
-(25年-06月)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -46896,7 +46896,7 @@
           <t>F | 447呎 (2房)
 $863万
 $19,315/呎
-(25年-06月)</t>
+(25年-06月-19日)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -46904,7 +46904,7 @@
           <t>G | 437呎 (2房)
 $802万
 $18,348/呎
-(25年-06月)</t>
+(25年-06月-09日)</t>
         </is>
       </c>
     </row>
@@ -46919,7 +46919,7 @@
           <t>A | 493呎 (2房)
 $929万
 $18,838/呎
-(25年-01月)</t>
+(25年-01月-09日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -46927,7 +46927,7 @@
           <t>B | 305呎 (1房)
 $538万
 $17,652/呎
-(24年-12月)</t>
+(24年-12月-16日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -46935,7 +46935,7 @@
           <t>C | 305呎 (1房)
 $544万
 $17,846/呎
-(25年-01月)</t>
+(25年-01月-14日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -46943,7 +46943,7 @@
           <t>D | 305呎 (1房)
 $550万
 $18,043/呎
-(25年-05月)</t>
+(25年-05月-20日)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -46951,7 +46951,7 @@
           <t>E | 301呎 (1房)
 $571万
 $18,980/呎
-(25年-06月)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -46959,7 +46959,7 @@
           <t>F | 447呎 (2房)
 $859万
 $19,219/呎
-(25年-04月)</t>
+(25年-04月-16日)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -46967,7 +46967,7 @@
           <t>G | 437呎 (2房)
 $798万
 $18,256/呎
-(25年-05月)</t>
+(25年-05月-20日)</t>
         </is>
       </c>
     </row>
@@ -46982,7 +46982,7 @@
           <t>A | 493呎 (2房)
 $924万
 $18,744/呎
-(25年-04月)</t>
+(25年-04月-16日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -46990,7 +46990,7 @@
           <t>B | 305呎 (1房)
 $536万
 $17,564/呎
-(24年-12月)</t>
+(24年-12月-16日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -46998,7 +46998,7 @@
           <t>C | 305呎 (1房)
 $542万
 $17,757/呎
-(25年-03月)</t>
+(25年-03月-13日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -47006,7 +47006,7 @@
           <t>D | 305呎 (1房)
 $548万
 $17,951/呎
-(25年-05月)</t>
+(25年-05月-19日)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -47014,7 +47014,7 @@
           <t>E | 301呎 (1房)
 $568万
 $18,884/呎
-(25年-06月)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -47022,7 +47022,7 @@
           <t>F | 447呎 (2房)
 $855万
 $19,123/呎
-(25年-07月)</t>
+(25年-07月-21日)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -47030,7 +47030,7 @@
           <t>G | 437呎 (2房)
 $794万
 $18,162/呎
-(25年-05月)</t>
+(25年-05月-06日)</t>
         </is>
       </c>
     </row>
@@ -47045,7 +47045,7 @@
           <t>A | 493呎 (2房)
 $920万
 $18,651/呎
-(25年-03月)</t>
+(25年-03月-06日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -47053,7 +47053,7 @@
           <t>B | 305呎 (1房)
 $533万
 $17,475/呎
-(24年-12月)</t>
+(24年-12月-30日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -47061,7 +47061,7 @@
           <t>C | 305呎 (1房)
 $539万
 $17,669/呎
-(25年-04月)</t>
+(25年-04月-01日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -47069,7 +47069,7 @@
           <t>D | 305呎 (1房)
 $557万
 $18,259/呎
-(25年-06月)</t>
+(25年-06月-01日)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -47077,7 +47077,7 @@
           <t>E | 301呎 (1房)
 $560万
 $18,608/呎
-(25年-06月)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -47085,7 +47085,7 @@
           <t>F | 447呎 (2房)
 $851万
 $19,029/呎
-(25年-07月)</t>
+(25年-07月-21日)</t>
         </is>
       </c>
       <c r="H21" s="23" t="inlineStr">
@@ -47108,7 +47108,7 @@
           <t>A | 493呎 (2房)
 $909万
 $18,442/呎
-(25年-02月)</t>
+(25年-02月-26日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -47116,7 +47116,7 @@
           <t>B | 305呎 (1房)
 $529万
 $17,351/呎
-(25年-01月)</t>
+(25年-01月-05日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -47124,7 +47124,7 @@
           <t>C | 305呎 (1房)
 $535万
 $17,544/呎
-(25年-03月)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -47132,7 +47132,7 @@
           <t>D | 305呎 (1房)
 $541万
 $17,734/呎
-(25年-05月)</t>
+(25年-05月-06日)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -47140,7 +47140,7 @@
           <t>E | 301呎 (1房)
 $556万
 $18,475/呎
-(25年-06月)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -47148,7 +47148,7 @@
           <t>F | 447呎 (2房)
 $850万
 $19,007/呎
-(25年-07月)</t>
+(25年-07月-23日)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -47156,7 +47156,7 @@
           <t>G | 437呎 (2房)
 $789万
 $18,055/呎
-(25年-06月)</t>
+(25年-06月-10日)</t>
         </is>
       </c>
     </row>
@@ -47171,7 +47171,7 @@
           <t>A | 493呎 (2房)
 $905万
 $18,357/呎
-(25年-01月)</t>
+(25年-01月-13日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -47179,7 +47179,7 @@
           <t>B | 305呎 (1房)
 $526万
 $17,233/呎
-(25年-01月)</t>
+(25年-01月-05日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -47187,7 +47187,7 @@
           <t>C | 305呎 (1房)
 $531万
 $17,423/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -47195,7 +47195,7 @@
           <t>D | 305呎 (1房)
 $537万
 $17,613/呎
-(25年-05月)</t>
+(25年-05月-19日)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -47203,7 +47203,7 @@
           <t>E | 301呎 (1房)
 $552万
 $18,346/呎
-(25年-06月)</t>
+(25年-06月-22日)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -47211,7 +47211,7 @@
           <t>F | 447呎 (2房)
 $849万
 $18,998/呎
-(25年-08月)</t>
+(25年-08月-20日)</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
@@ -47219,7 +47219,7 @@
           <t>G | 437呎 (2房)
 $786万
 $17,995/呎
-(25年-05月)</t>
+(25年-05月-18日)</t>
         </is>
       </c>
     </row>
@@ -47234,7 +47234,7 @@
           <t>A | 493呎 (2房)
 $898万
 $18,207/呎
-(25年-06月)</t>
+(25年-06月-12日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -47242,7 +47242,7 @@
           <t>B | 305呎 (1房)
 $522万
 $17,111/呎
-(25年-01月)</t>
+(25年-01月-05日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -47250,7 +47250,7 @@
           <t>C | 305呎 (1房)
 $528万
 $17,302/呎
-(25年-05月)</t>
+(25年-05月-26日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -47258,7 +47258,7 @@
           <t>D | 305呎 (1房)
 $533万
 $17,489/呎
-(25年-05月)</t>
+(25年-05月-25日)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -47266,7 +47266,7 @@
           <t>E | 301呎 (1房)
 $548万
 $18,219/呎
-(25年-06月)</t>
+(25年-06月-29日)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -47274,7 +47274,7 @@
           <t>F | 447呎 (2房)
 $840万
 $18,792/呎
-(25年-10月)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr">
@@ -47282,7 +47282,7 @@
           <t>G | 437呎 (2房)
 $780万
 $17,854/呎
-(25年-07月)</t>
+(25年-07月-01日)</t>
         </is>
       </c>
     </row>
@@ -47297,7 +47297,7 @@
           <t>A | 493呎 (2房)
 $885万
 $17,955/呎
-(25年-06月)</t>
+(25年-06月-25日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -47305,7 +47305,7 @@
           <t>B | 305呎 (1房)
 $518万
 $16,990/呎
-(25年-01月)</t>
+(25年-01月-05日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -47313,7 +47313,7 @@
           <t>C | 305呎 (1房)
 $524万
 $17,180/呎
-(25年-04月)</t>
+(25年-04月-01日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -47321,7 +47321,7 @@
           <t>D | 305呎 (1房)
 $530万
 $17,367/呎
-(25年-05月)</t>
+(25年-05月-05日)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -47329,7 +47329,7 @@
           <t>E | 301呎 (1房)
 $540万
 $17,930/呎
-(25年-06月)</t>
+(25年-06月-09日)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -47337,7 +47337,7 @@
           <t>F | 447呎 (2房)
 $826万
 $18,479/呎
-(25年-11月)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
       <c r="H25" s="20" t="inlineStr">
@@ -47345,7 +47345,7 @@
           <t>G | 437呎 (2房)
 $767万
 $17,556/呎
-(25年-07月)</t>
+(25年-07月-01日)</t>
         </is>
       </c>
     </row>
@@ -47360,7 +47360,7 @@
           <t>A | 493呎 (2房)
 $876万
 $17,779/呎
-(25年-08月)</t>
+(25年-08月-18日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -47368,7 +47368,7 @@
           <t>B | 305呎 (1房)
 $515万
 $16,872/呎
-(25年-01月)</t>
+(25年-01月-05日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -47376,7 +47376,7 @@
           <t>C | 305呎 (1房)
 $520万
 $17,056/呎
-(25年-06月)</t>
+(25年-06月-03日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -47384,7 +47384,7 @@
           <t>D | 305呎 (1房)
 $529万
 $17,341/呎
-(25年-06月)</t>
+(25年-06月-15日)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -47392,7 +47392,7 @@
           <t>E | 301呎 (1房)
 $530万
 $17,611/呎
-(25年-06月)</t>
+(25年-06月-09日)</t>
         </is>
       </c>
       <c r="G26" s="24" t="inlineStr">
@@ -47408,7 +47408,7 @@
           <t>G | 437呎 (2房)
 $757万
 $17,327/呎
-(25年-07月)</t>
+(25年-07月-30日)</t>
         </is>
       </c>
     </row>
@@ -47423,7 +47423,7 @@
           <t>A | 493呎 (2房)
 $854万
 $17,312/呎
-(25年-06月)</t>
+(25年-06月-23日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -47431,7 +47431,7 @@
           <t>B | 305呎 (1房)
 $514万
 $16,846/呎
-(25年-06月)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -47439,7 +47439,7 @@
           <t>C | 305呎 (1房)
 $520万
 $17,033/呎
-(25年-06月)</t>
+(25年-06月-18日)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -47447,7 +47447,7 @@
           <t>D | 305呎 (1房)
 $531万
 $17,410/呎
-(25年-06月)</t>
+(25年-06月-01日)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -47455,7 +47455,7 @@
           <t>E | 301呎 (1房)
 $526万
 $17,488/呎
-(25年-06月)</t>
+(25年-06月-08日)</t>
         </is>
       </c>
       <c r="G27" s="24" t="inlineStr">
@@ -47471,7 +47471,7 @@
           <t>G | 437呎 (2房)
 $746万
 $17,071/呎
-(25年-10月)</t>
+(25年-10月-05日)</t>
         </is>
       </c>
     </row>
@@ -47486,7 +47486,7 @@
           <t>A | 493呎 (2房)
 $838万
 $17,008/呎
-(25年-10月)</t>
+(25年-10月-05日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -47494,7 +47494,7 @@
           <t>B | 305呎 (1房)
 $513万
 $16,820/呎
-(25年-06月)</t>
+(25年-06月-23日)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -47502,7 +47502,7 @@
           <t>C | 305呎 (1房)
 $519万
 $17,007/呎
-(25年-08月)</t>
+(25年-08月-05日)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -47510,7 +47510,7 @@
           <t>D | 305呎 (1房)
 $524万
 $17,193/呎
-(25年-07月)</t>
+(25年-07月-28日)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -47518,7 +47518,7 @@
           <t>E | 301呎 (1房)
 $523万
 $17,369/呎
-(25年-06月)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="G28" s="24" t="inlineStr">
@@ -47534,7 +47534,7 @@
           <t>G | 437呎 (2房)
 $733万
 $16,767/呎
-(25年-10月)</t>
+(25年-10月-23日)</t>
         </is>
       </c>
     </row>
@@ -47696,7 +47696,7 @@
           <t>A | 440呎 (2房)
 $1072万
 $24,361/呎
-(26年-03月)</t>
+(26年-03月-29日)</t>
         </is>
       </c>
       <c r="C5" s="22" t="inlineStr">
@@ -47720,7 +47720,7 @@
           <t>D | 245呎 (开放式)
 $554万
 $22,604/呎
-(26年-03月)</t>
+(26年-03月-25日)</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
@@ -47728,7 +47728,7 @@
           <t>E | 246呎 (开放式)
 $474万
 $19,252/呎
-(25年-10月)</t>
+(25年-10月-22日)</t>
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
@@ -47736,7 +47736,7 @@
           <t>F | 246呎 (开放式)
 $476万
 $19,362/呎
-(25年-10月)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="H5" s="20" t="inlineStr">
@@ -47744,7 +47744,7 @@
           <t>G | 300呎 (1房)
 $583万
 $19,427/呎
-(25年-07月)</t>
+(25年-07月-28日)</t>
         </is>
       </c>
       <c r="I5" s="24" t="inlineStr">
@@ -47767,7 +47767,7 @@
           <t>A | 440呎 (2房)
 $907万
 $20,620/呎
-(25年-11月)</t>
+(25年-11月-05日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -47791,7 +47791,7 @@
           <t>D | 245呎 (开放式)
 $487万
 $19,890/呎
-(25年-11月)</t>
+(25年-11月-04日)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -47799,7 +47799,7 @@
           <t>E | 246呎 (开放式)
 $469万
 $19,061/呎
-(25年-10月)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -47807,7 +47807,7 @@
           <t>F | 246呎 (开放式)
 $472万
 $19,167/呎
-(25年-10月)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
@@ -47815,7 +47815,7 @@
           <t>G | 300呎 (1房)
 $577万
 $19,230/呎
-(25年-07月)</t>
+(25年-07月-01日)</t>
         </is>
       </c>
       <c r="I6" s="24" t="inlineStr">
@@ -47838,7 +47838,7 @@
           <t>A | 440呎 (2房)
 $909万
 $20,655/呎
-(25年-10月)</t>
+(25年-10月-23日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -47862,7 +47862,7 @@
           <t>D | 245呎 (开放式)
 $482万
 $19,694/呎
-(25年-11月)</t>
+(25年-11月-04日)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -47870,7 +47870,7 @@
           <t>E | 246呎 (开放式)
 $464万
 $18,866/呎
-(25年-10月)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -47878,7 +47878,7 @@
           <t>F | 246呎 (开放式)
 $467万
 $18,980/呎
-(25年-09月)</t>
+(25年-09月-06日)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -47886,7 +47886,7 @@
           <t>G | 300呎 (1房)
 $571万
 $19,043/呎
-(25年-07月)</t>
+(25年-07月-03日)</t>
         </is>
       </c>
       <c r="I7" s="21" t="inlineStr">
@@ -47909,7 +47909,7 @@
           <t>A | 440呎 (2房)
 $889万
 $20,214/呎
-(25年-08月)</t>
+(25年-08月-31日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -47933,7 +47933,7 @@
           <t>D | 245呎 (开放式)
 $478万
 $19,498/呎
-(25年-11月)</t>
+(25年-11月-03日)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -47941,7 +47941,7 @@
           <t>E | 246呎 (开放式)
 $454万
 $18,476/呎
-(25年-09月)</t>
+(25年-09月-08日)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -47949,7 +47949,7 @@
           <t>F | 246呎 (开放式)
 $462万
 $18,793/呎
-(25年-09月)</t>
+(25年-09月-07日)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -47957,7 +47957,7 @@
           <t>G | 300呎 (1房)
 $566万
 $18,853/呎
-(25年-06月)</t>
+(25年-06月-29日)</t>
         </is>
       </c>
       <c r="I8" s="21" t="inlineStr">
@@ -47980,7 +47980,7 @@
           <t>A | 440呎 (2房)
 $881万
 $20,014/呎
-(25年-08月)</t>
+(25年-08月-27日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -48004,7 +48004,7 @@
           <t>D | 245呎 (开放式)
 $468万
 $19,098/呎
-(25年-10月)</t>
+(25年-10月-22日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -48012,7 +48012,7 @@
           <t>E | 246呎 (开放式)
 $450万
 $18,293/呎
-(25年-06月)</t>
+(25年-06月-25日)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -48020,7 +48020,7 @@
           <t>F | 246呎 (开放式)
 $458万
 $18,602/呎
-(25年-10月)</t>
+(25年-10月-01日)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -48028,7 +48028,7 @@
           <t>G | 300呎 (1房)
 $560万
 $18,667/呎
-(25年-06月)</t>
+(25年-06月-19日)</t>
         </is>
       </c>
       <c r="I9" s="21" t="inlineStr">
@@ -48051,7 +48051,7 @@
           <t>A | 440呎 (2房)
 $886万
 $20,148/呎
-(25年-07月)</t>
+(25年-07月-29日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -48075,7 +48075,7 @@
           <t>D | 245呎 (开放式)
 $460万
 $18,792/呎
-(25年-10月)</t>
+(25年-10月-23日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -48083,7 +48083,7 @@
           <t>E | 246呎 (开放式)
 $448万
 $18,207/呎
-(25年-07月)</t>
+(25年-07月-29日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -48091,7 +48091,7 @@
           <t>F | 246呎 (开放式)
 $450万
 $18,305/呎
-(25年-08月)</t>
+(25年-08月-25日)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -48099,7 +48099,7 @@
           <t>G | 300呎 (1房)
 $557万
 $18,570/呎
-(25年-06月)</t>
+(25年-06月-19日)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -48107,7 +48107,7 @@
           <t>H | 493呎 (2房)
 $1059万
 $21,473/呎
-(25年-10月)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
     </row>
@@ -48122,7 +48122,7 @@
           <t>A | 440呎 (2房)
 $882万
 $20,048/呎
-(25年-09月)</t>
+(25年-09月-09日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -48146,7 +48146,7 @@
           <t>D | 245呎 (开放式)
 $458万
 $18,698/呎
-(25年-10月)</t>
+(25年-10月-23日)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -48154,7 +48154,7 @@
           <t>E | 247呎 (开放式)
 $446万
 $18,036/呎
-(25年-06月)</t>
+(25年-06月-12日)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -48162,7 +48162,7 @@
           <t>F | 246呎 (开放式)
 $448万
 $18,220/呎
-(25年-09月)</t>
+(25年-09月-04日)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -48170,7 +48170,7 @@
           <t>G | 300呎 (1房)
 $554万
 $18,480/呎
-(25年-06月)</t>
+(25年-06月-09日)</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -48178,7 +48178,7 @@
           <t>H | 493呎 (2房)
 $1030万
 $20,895/呎
-(25年-12月)</t>
+(25年-12月-21日)</t>
         </is>
       </c>
     </row>
@@ -48264,7 +48264,7 @@
           <t>A | 440呎 (2房)
 $863万
 $19,616/呎
-(25年-06月)</t>
+(25年-06月-29日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -48288,7 +48288,7 @@
           <t>D | 245呎 (开放式)
 $466万
 $19,029/呎
-(25年-11月)</t>
+(25年-11月-03日)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -48296,7 +48296,7 @@
           <t>E | 247呎 (开放式)
 $441万
 $17,862/呎
-(25年-07月)</t>
+(25年-07月-13日)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -48304,7 +48304,7 @@
           <t>F | 246呎 (开放式)
 $444万
 $18,037/呎
-(25年-09月)</t>
+(25年-09月-15日)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -48312,7 +48312,7 @@
           <t>G | 300呎 (1房)
 $549万
 $18,300/呎
-(25年-01月)</t>
+(25年-01月-20日)</t>
         </is>
       </c>
       <c r="I13" s="20" t="inlineStr">
@@ -48320,7 +48320,7 @@
           <t>H | 493呎 (2房)
 $1020万
 $20,688/呎
-(25年-08月)</t>
+(25年-08月-18日)</t>
         </is>
       </c>
     </row>
@@ -48335,7 +48335,7 @@
           <t>A | 440呎 (2房)
 $859万
 $19,520/呎
-(25年-07月)</t>
+(25年-07月-23日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -48359,7 +48359,7 @@
           <t>D | 245呎 (开放式)
 $464万
 $18,931/呎
-(25年-11月)</t>
+(25年-11月-04日)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -48367,7 +48367,7 @@
           <t>E | 246呎 (开放式)
 $439万
 $17,846/呎
-(25年-07月)</t>
+(25年-07月-15日)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -48375,7 +48375,7 @@
           <t>F | 246呎 (开放式)
 $442万
 $17,947/呎
-(25年-09月)</t>
+(25年-09月-08日)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -48383,7 +48383,7 @@
           <t>G | 300呎 (1房)
 $546万
 $18,207/呎
-(25年-04月)</t>
+(25年-04月-14日)</t>
         </is>
       </c>
       <c r="I14" s="20" t="inlineStr">
@@ -48391,7 +48391,7 @@
           <t>H | 493呎 (2房)
 $1015万
 $20,584/呎
-(25年-07月)</t>
+(25年-07月-13日)</t>
         </is>
       </c>
     </row>
@@ -48406,7 +48406,7 @@
           <t>A | 440呎 (2房)
 $855万
 $19,423/呎
-(25年-08月)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -48430,7 +48430,7 @@
           <t>D | 245呎 (开放式)
 $462万
 $18,841/呎
-(25年-11月)</t>
+(25年-11月-04日)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -48438,7 +48438,7 @@
           <t>E | 247呎 (开放式)
 $437万
 $17,684/呎
-(25年-07月)</t>
+(25年-07月-16日)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -48446,7 +48446,7 @@
           <t>F | 246呎 (开放式)
 $444万
 $18,053/呎
-(25年-09月)</t>
+(25年-09月-16日)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -48454,7 +48454,7 @@
           <t>G | 300呎 (1房)
 $544万
 $18,117/呎
-(25年-05月)</t>
+(25年-05月-05日)</t>
         </is>
       </c>
       <c r="I15" s="20" t="inlineStr">
@@ -48462,7 +48462,7 @@
           <t>H | 493呎 (2房)
 $1010万
 $20,483/呎
-(25年-08月)</t>
+(25年-08月-17日)</t>
         </is>
       </c>
     </row>
@@ -48477,7 +48477,7 @@
           <t>A | 440呎 (2房)
 $850万
 $19,327/呎
-(25年-07月)</t>
+(25年-07月-31日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -48501,7 +48501,7 @@
           <t>D | 245呎 (开放式)
 $447万
 $18,237/呎
-(25年-10月)</t>
+(25年-10月-26日)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -48509,7 +48509,7 @@
           <t>E | 246呎 (开放式)
 $435万
 $17,671/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -48517,7 +48517,7 @@
           <t>F | 246呎 (开放式)
 $437万
 $17,768/呎
-(25年-08月)</t>
+(25年-08月-17日)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -48525,7 +48525,7 @@
           <t>G | 300呎 (1房)
 $541万
 $18,027/呎
-(25年-05月)</t>
+(25年-05月-01日)</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -48533,7 +48533,7 @@
           <t>H | 493呎 (2房)
 $1005万
 $20,379/呎
-(25年-12月)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
     </row>
@@ -48548,7 +48548,7 @@
           <t>A | 440呎 (2房)
 $846万
 $19,230/呎
-(25年-07月)</t>
+(25年-07月-14日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -48572,7 +48572,7 @@
           <t>D | 245呎 (开放式)
 $445万
 $18,147/呎
-(25年-10月)</t>
+(25年-10月-27日)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -48580,7 +48580,7 @@
           <t>E | 247呎 (开放式)
 $432万
 $17,510/呎
-(25年-04月)</t>
+(25年-04月-16日)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -48588,7 +48588,7 @@
           <t>F | 246呎 (开放式)
 $435万
 $17,679/呎
-(25年-09月)</t>
+(25年-09月-02日)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -48596,7 +48596,7 @@
           <t>G | 300呎 (1房)
 $538万
 $17,937/呎
-(25年-01月)</t>
+(25年-01月-12日)</t>
         </is>
       </c>
       <c r="I17" s="20" t="inlineStr">
@@ -48604,7 +48604,7 @@
           <t>H | 493呎 (2房)
 $1000万
 $20,278/呎
-(25年-09月)</t>
+(25年-09月-28日)</t>
         </is>
       </c>
     </row>
@@ -48619,7 +48619,7 @@
           <t>A | 440呎 (2房)
 $822万
 $18,684/呎
-(25年-01月)</t>
+(25年-01月-07日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -48643,7 +48643,7 @@
           <t>D | 245呎 (开放式)
 $457万
 $18,657/呎
-(25年-11月)</t>
+(25年-11月-04日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -48651,7 +48651,7 @@
           <t>E | 247呎 (开放式)
 $430万
 $17,417/呎
-(25年-05月)</t>
+(25年-05月-07日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -48659,7 +48659,7 @@
           <t>F | 246呎 (开放式)
 $433万
 $17,593/呎
-(25年-09月)</t>
+(25年-09月-08日)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -48667,7 +48667,7 @@
           <t>G | 300呎 (1房)
 $535万
 $17,847/呎
-(25年-01月)</t>
+(25年-01月-07日)</t>
         </is>
       </c>
       <c r="I18" s="20" t="inlineStr">
@@ -48675,7 +48675,7 @@
           <t>H | 493呎 (2房)
 $1006万
 $20,404/呎
-(25年-07月)</t>
+(25年-07月-14日)</t>
         </is>
       </c>
     </row>
@@ -48690,7 +48690,7 @@
           <t>A | 440呎 (2房)
 $818万
 $18,589/呎
-(25年-05月)</t>
+(25年-05月-27日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -48714,7 +48714,7 @@
           <t>D | 245呎 (开放式)
 $455万
 $18,563/呎
-(25年-11月)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -48722,7 +48722,7 @@
           <t>E | 246呎 (开放式)
 $428万
 $17,402/呎
-(25年-06月)</t>
+(25年-06月-26日)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -48730,7 +48730,7 @@
           <t>F | 246呎 (开放式)
 $431万
 $17,504/呎
-(25年-09月)</t>
+(25年-09月-04日)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -48738,7 +48738,7 @@
           <t>G | 300呎 (1房)
 $533万
 $17,757/呎
-(24年-12月)</t>
+(24年-12月-16日)</t>
         </is>
       </c>
       <c r="I19" s="20" t="inlineStr">
@@ -48746,7 +48746,7 @@
           <t>H | 493呎 (2房)
 $990万
 $20,075/呎
-(25年-10月)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
     </row>
@@ -48761,7 +48761,7 @@
           <t>A | 440呎 (2房)
 $814万
 $18,498/呎
-(25年-06月)</t>
+(25年-06月-12日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -48785,7 +48785,7 @@
           <t>D | 245呎 (开放式)
 $453万
 $18,473/呎
-(25年-11月)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -48793,7 +48793,7 @@
           <t>E | 246呎 (开放式)
 $426万
 $17,317/呎
-(25年-06月)</t>
+(25年-06月-25日)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -48801,7 +48801,7 @@
           <t>F | 246呎 (开放式)
 $428万
 $17,415/呎
-(25年-09月)</t>
+(25年-09月-04日)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -48809,7 +48809,7 @@
           <t>G | 300呎 (1房)
 $530万
 $17,667/呎
-(25年-01月)</t>
+(25年-01月-06日)</t>
         </is>
       </c>
       <c r="I20" s="20" t="inlineStr">
@@ -48817,7 +48817,7 @@
           <t>H | 493呎 (2房)
 $985万
 $19,976/呎
-(25年-07月)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
     </row>
@@ -48832,7 +48832,7 @@
           <t>A | 440呎 (2房)
 $810万
 $18,405/呎
-(25年-04月)</t>
+(25年-04月-06日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -48856,7 +48856,7 @@
           <t>D | 245呎 (开放式)
 $450万
 $18,380/呎
-(25年-11月)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -48864,7 +48864,7 @@
           <t>E | 247呎 (开放式)
 $424万
 $17,162/呎
-(25年-06月)</t>
+(25年-06月-26日)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -48872,7 +48872,7 @@
           <t>F | 246呎 (开放式)
 $426万
 $17,329/呎
-(25年-08月)</t>
+(25年-08月-11日)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -48880,7 +48880,7 @@
           <t>G | 300呎 (1房)
 $527万
 $17,580/呎
-(24年-12月)</t>
+(24年-12月-16日)</t>
         </is>
       </c>
       <c r="I21" s="20" t="inlineStr">
@@ -48888,7 +48888,7 @@
           <t>H | 493呎 (2房)
 $980万
 $19,874/呎
-(25年-07月)</t>
+(25年-07月-01日)</t>
         </is>
       </c>
     </row>
@@ -48903,7 +48903,7 @@
           <t>A | 440呎 (2房)
 $809万
 $18,384/呎
-(25年-07月)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -48927,7 +48927,7 @@
           <t>D | 245呎 (开放式)
 $442万
 $18,057/呎
-(25年-11月)</t>
+(25年-11月-02日)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -48935,7 +48935,7 @@
           <t>E | 247呎 (开放式)
 $421万
 $17,040/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -48943,7 +48943,7 @@
           <t>F | 246呎 (开放式)
 $423万
 $17,207/呎
-(25年-09月)</t>
+(25年-09月-02日)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -48951,7 +48951,7 @@
           <t>G | 300呎 (1房)
 $524万
 $17,457/呎
-(25年-01月)</t>
+(25年-01月-01日)</t>
         </is>
       </c>
       <c r="I22" s="21" t="inlineStr">
@@ -48974,7 +48974,7 @@
           <t>A | 440呎 (2房)
 $808万
 $18,359/呎
-(25年-06月)</t>
+(25年-06月-29日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -48998,7 +48998,7 @@
           <t>D | 245呎 (开放式)
 $439万
 $17,931/呎
-(25年-11月)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -49006,7 +49006,7 @@
           <t>E | 247呎 (开放式)
 $418万
 $16,919/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -49014,7 +49014,7 @@
           <t>F | 246呎 (开放式)
 $420万
 $17,085/呎
-(25年-09月)</t>
+(25年-09月-02日)</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
@@ -49022,7 +49022,7 @@
           <t>G | 300呎 (1房)
 $520万
 $17,333/呎
-(25年-01月)</t>
+(25年-01月-01日)</t>
         </is>
       </c>
       <c r="I23" s="21" t="inlineStr">
@@ -49045,7 +49045,7 @@
           <t>A | 440呎 (2房)
 $800万
 $18,177/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -49062,7 +49062,7 @@
           <t>D | 251呎 (开放式)
 $491万
 $19,546/呎
-(26年-03月)</t>
+(26年-03月-25日)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -49070,7 +49070,7 @@
           <t>E | 247呎 (开放式)
 $415万
 $16,798/呎
-(25年-04月)</t>
+(25年-04月-23日)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -49078,7 +49078,7 @@
           <t>F | 246呎 (开放式)
 $417万
 $16,967/呎
-(25年-09月)</t>
+(25年-09月-04日)</t>
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr">
@@ -49086,7 +49086,7 @@
           <t>G | 300呎 (1房)
 $516万
 $17,213/呎
-(25年-01月)</t>
+(25年-01月-01日)</t>
         </is>
       </c>
       <c r="I24" s="24" t="inlineStr">
@@ -49109,7 +49109,7 @@
           <t>A | 440呎 (2房)
 $785万
 $17,845/呎
-(25年-09月)</t>
+(25年-09月-18日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -49126,7 +49126,7 @@
           <t>D | 251呎 (开放式)
 $438万
 $17,438/呎
-(25年-12月)</t>
+(25年-12月-01日)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -49134,7 +49134,7 @@
           <t>E | 247呎 (开放式)
 $412万
 $16,684/呎
-(25年-04月)</t>
+(25年-04月-23日)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -49142,7 +49142,7 @@
           <t>F | 246呎 (开放式)
 $414万
 $16,850/呎
-(25年-09月)</t>
+(25年-09月-17日)</t>
         </is>
       </c>
       <c r="H25" s="20" t="inlineStr">
@@ -49150,7 +49150,7 @@
           <t>G | 300呎 (1房)
 $513万
 $17,093/呎
-(25年-01月)</t>
+(25年-01月-01日)</t>
         </is>
       </c>
       <c r="I25" s="20" t="inlineStr">
@@ -49158,7 +49158,7 @@
           <t>H | 493呎 (2房)
 $955万
 $19,363/呎
-(25年-12月)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
     </row>
@@ -49173,7 +49173,7 @@
           <t>A | 440呎 (2房)
 $774万
 $17,584/呎
-(25年-07月)</t>
+(25年-07月-23日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -49190,7 +49190,7 @@
           <t>D | 251呎 (开放式)
 $435万
 $17,315/呎
-(25年-11月)</t>
+(25年-11月-09日)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -49198,7 +49198,7 @@
           <t>E | 247呎 (开放式)
 $412万
 $16,660/呎
-(25年-07月)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -49206,7 +49206,7 @@
           <t>F | 246呎 (开放式)
 $414万
 $16,821/呎
-(25年-09月)</t>
+(25年-09月-21日)</t>
         </is>
       </c>
       <c r="H26" s="20" t="inlineStr">
@@ -49214,7 +49214,7 @@
           <t>G | 300呎 (1房)
 $509万
 $16,973/呎
-(25年-01月)</t>
+(25年-01月-01日)</t>
         </is>
       </c>
       <c r="I26" s="21" t="inlineStr">
@@ -49237,7 +49237,7 @@
           <t>A | 440呎 (2房)
 $761万
 $17,295/呎
-(25年-11月)</t>
+(25年-11月-03日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -49254,7 +49254,7 @@
           <t>D | 251呎 (开放式)
 $432万
 $17,195/呎
-(25年-11月)</t>
+(25年-11月-09日)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -49262,7 +49262,7 @@
           <t>E | 247呎 (开放式)
 $409万
 $16,547/呎
-(25年-07月)</t>
+(25年-07月-06日)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -49270,7 +49270,7 @@
           <t>F | 246呎 (开放式)
 $411万
 $16,703/呎
-(25年-08月)</t>
+(25年-08月-17日)</t>
         </is>
       </c>
       <c r="H27" s="20" t="inlineStr">
@@ -49278,7 +49278,7 @@
           <t>G | 300呎 (1房)
 $506万
 $16,853/呎
-(25年-01月)</t>
+(25年-01月-07日)</t>
         </is>
       </c>
       <c r="I27" s="21" t="inlineStr">
@@ -49301,7 +49301,7 @@
           <t>A | 440呎 (2房)
 $747万
 $16,975/呎
-(25年-12月)</t>
+(25年-12月-22日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -49318,7 +49318,7 @@
           <t>D | 251呎 (开放式)
 $477万
 $19,008/呎
-(26年-03月)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -49326,7 +49326,7 @@
           <t>E | 247呎 (开放式)
 $408万
 $16,514/呎
-(25年-07月)</t>
+(25年-07月-10日)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">
@@ -49334,7 +49334,7 @@
           <t>F | 246呎 (开放式)
 $410万
 $16,683/呎
-(25年-09月)</t>
+(25年-09月-15日)</t>
         </is>
       </c>
       <c r="H28" s="20" t="inlineStr">
@@ -49342,7 +49342,7 @@
           <t>G | 300呎 (1房)
 $502万
 $16,737/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="I28" s="24" t="inlineStr">
@@ -49530,7 +49530,7 @@
           <t>D | 305呎 (1房)
 $654万
 $21,439/呎
-(25年-12月)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="F5" s="22" t="inlineStr">
@@ -49593,7 +49593,7 @@
           <t>D | 305呎 (1房)
 $648万
 $21,230/呎
-(25年-11月)</t>
+(25年-11月-27日)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -49656,7 +49656,7 @@
           <t>D | 305呎 (1房)
 $641万
 $21,016/呎
-(25年-11月)</t>
+(25年-11月-04日)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -49711,7 +49711,7 @@
           <t>C | 244呎 (开放式)
 $574万
 $23,525/呎
-(26年-06月)</t>
+(26年-06月-19日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -49719,7 +49719,7 @@
           <t>D | 305呎 (1房)
 $621万
 $20,357/呎
-(25年-08月)</t>
+(25年-08月-31日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -49758,7 +49758,7 @@
           <t>A | 439呎 (2房)
 $1096万
 $24,970/呎
-(25年-08月)</t>
+(25年-08月-21日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -49774,7 +49774,7 @@
           <t>C | 244呎 (开放式)
 $557万
 $22,836/呎
-(26年-05月)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -49782,7 +49782,7 @@
           <t>D | 305呎 (1房)
 $615万
 $20,154/呎
-(25年-08月)</t>
+(25年-08月-31日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -49821,7 +49821,7 @@
           <t>A | 440呎 (2房)
 $1319万
 $29,982/呎
-(26年-06月)</t>
+(26年-06月-30日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -49837,7 +49837,7 @@
           <t>C | 244呎 (开放式)
 $552万
 $22,611/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -49845,7 +49845,7 @@
           <t>D | 305呎 (1房)
 $609万
 $19,954/呎
-(25年-09月)</t>
+(25年-09月-01日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -49884,7 +49884,7 @@
           <t>A | 439呎 (2房)
 $1274万
 $29,027/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -49900,7 +49900,7 @@
           <t>C | 244呎 (开放式)
 $543万
 $22,270/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -49908,7 +49908,7 @@
           <t>D | 305呎 (1房)
 $606万
 $19,856/呎
-(25年-07月)</t>
+(25年-07月-27日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -49932,7 +49932,7 @@
           <t>G | 494呎 (2房)
 $1301万
 $26,342/呎
-(25年-12月)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
     </row>
@@ -49947,7 +49947,7 @@
           <t>A | 439呎 (2房)
 $1075万
 $24,478/呎
-(25年-08月)</t>
+(25年-08月-21日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -49963,7 +49963,7 @@
           <t>C | 244呎 (开放式)
 $547万
 $22,406/呎
-(26年-04月)</t>
+(26年-04月-07日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -49971,7 +49971,7 @@
           <t>D | 305呎 (1房)
 $603万
 $19,757/呎
-(25年-07月)</t>
+(25年-07月-27日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -50089,7 +50089,7 @@
           <t>C | 244呎 (开放式)
 $541万
 $22,164/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -50097,7 +50097,7 @@
           <t>D | 305呎 (1房)
 $597万
 $19,564/呎
-(25年-07月)</t>
+(25年-07月-27日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -50152,7 +50152,7 @@
           <t>C | 244呎 (开放式)
 $550万
 $22,541/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -50160,7 +50160,7 @@
           <t>D | 305呎 (1房)
 $594万
 $19,466/呎
-(25年-07月)</t>
+(25年-07月-14日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -50215,7 +50215,7 @@
           <t>C | 244呎 (开放式)
 $542万
 $22,201/呎
-(26年-04月)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -50223,7 +50223,7 @@
           <t>D | 305呎 (1房)
 $591万
 $19,367/呎
-(25年-06月)</t>
+(25年-06月-25日)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -50231,7 +50231,7 @@
           <t>E | 305呎 (1房)
 $604万
 $19,797/呎
-(25年-09月)</t>
+(25年-09月-18日)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -50278,7 +50278,7 @@
           <t>C | 244呎 (开放式)
 $527万
 $21,615/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -50286,7 +50286,7 @@
           <t>D | 305呎 (1房)
 $588万
 $19,269/呎
-(25年-06月)</t>
+(25年-06月-19日)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -50294,7 +50294,7 @@
           <t>E | 305呎 (1房)
 $614万
 $20,128/呎
-(25年-09月)</t>
+(25年-09月-14日)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -50325,7 +50325,7 @@
           <t>A | 439呎 (2房)
 $1043万
 $23,756/呎
-(25年-11月)</t>
+(25年-11月-27日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -50349,7 +50349,7 @@
           <t>D | 305呎 (1房)
 $585万
 $19,177/呎
-(25年-07月)</t>
+(25年-07月-14日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -50357,7 +50357,7 @@
           <t>E | 305呎 (1房)
 $598万
 $19,600/呎
-(25年-09月)</t>
+(25年-09月-10日)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -50373,7 +50373,7 @@
           <t>G | 494呎 (2房)
 $1219万
 $24,678/呎
-(25年-12月)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
     </row>
@@ -50388,7 +50388,7 @@
           <t>A | 440呎 (2房)
 $1038万
 $23,584/呎
-(25年-05月)</t>
+(25年-05月-19日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -50412,7 +50412,7 @@
           <t>D | 305呎 (1房)
 $582万
 $19,079/呎
-(25年-07月)</t>
+(25年-07月-21日)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -50420,7 +50420,7 @@
           <t>E | 305呎 (1房)
 $595万
 $19,502/呎
-(25年-09月)</t>
+(25年-09月-21日)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -50436,7 +50436,7 @@
           <t>G | 494呎 (2房)
 $1213万
 $24,555/呎
-(25年-09月)</t>
+(25年-09月-25日)</t>
         </is>
       </c>
     </row>
@@ -50451,7 +50451,7 @@
           <t>A | 439呎 (2房)
 $1032万
 $23,519/呎
-(25年-11月)</t>
+(25年-11月-20日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -50475,7 +50475,7 @@
           <t>D | 305呎 (1房)
 $579万
 $18,984/呎
-(25年-07月)</t>
+(25年-07月-31日)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -50483,7 +50483,7 @@
           <t>E | 305呎 (1房)
 $645万
 $21,151/呎
-(26年-03月)</t>
+(26年-03月-17日)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -50499,7 +50499,7 @@
           <t>G | 494呎 (2房)
 $1387万
 $28,079/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
     </row>
@@ -50514,7 +50514,7 @@
           <t>A | 439呎 (2房)
 $1027万
 $23,401/呎
-(25年-12月)</t>
+(25年-12月-14日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -50530,7 +50530,7 @@
           <t>C | 244呎 (开放式)
 $525万
 $21,504/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -50538,7 +50538,7 @@
           <t>D | 305呎 (1房)
 $582万
 $19,098/呎
-(25年-07月)</t>
+(25年-07月-27日)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -50546,7 +50546,7 @@
           <t>E | 305呎 (1房)
 $589万
 $19,305/呎
-(25年-09月)</t>
+(25年-09月-04日)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -50562,7 +50562,7 @@
           <t>G | 494呎 (2房)
 $1380万
 $27,941/呎
-(26年-05月)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
     </row>
@@ -50577,7 +50577,7 @@
           <t>A | 440呎 (2房)
 $1022万
 $23,232/呎
-(25年-06月)</t>
+(25年-06月-10日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -50593,7 +50593,7 @@
           <t>C | 244呎 (开放式)
 $522万
 $21,402/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -50601,7 +50601,7 @@
           <t>D | 305呎 (1房)
 $573万
 $18,797/呎
-(25年-08月)</t>
+(25年-08月-20日)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -50609,7 +50609,7 @@
           <t>E | 305呎 (1房)
 $599万
 $19,626/呎
-(25年-09月)</t>
+(25年-09月-14日)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -50625,7 +50625,7 @@
           <t>G | 494呎 (2房)
 $1195万
 $24,188/呎
-(25年-06月)</t>
+(25年-06月-22日)</t>
         </is>
       </c>
     </row>
@@ -50656,7 +50656,7 @@
           <t>C | 244呎 (开放式)
 $516万
 $21,148/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -50664,7 +50664,7 @@
           <t>D | 305呎 (1房)
 $569万
 $18,662/呎
-(25年-08月)</t>
+(25年-08月-26日)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -50672,7 +50672,7 @@
           <t>E | 305呎 (1房)
 $594万
 $19,492/呎
-(25年-09月)</t>
+(25年-09月-14日)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -50719,7 +50719,7 @@
           <t>C | 244呎 (开放式)
 $509万
 $20,869/呎
-(26年-05月)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -50727,7 +50727,7 @@
           <t>D | 305呎 (1房)
 $563万
 $18,459/呎
-(25年-08月)</t>
+(25年-08月-11日)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -50735,7 +50735,7 @@
           <t>E | 305呎 (1房)
 $577万
 $18,905/呎
-(25年-09月)</t>
+(25年-09月-14日)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -50782,7 +50782,7 @@
           <t>C | 244呎 (开放式)
 $499万
 $20,467/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -50790,7 +50790,7 @@
           <t>D | 305呎 (1房)
 $554万
 $18,148/呎
-(25年-07月)</t>
+(25年-07月-20日)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -50798,7 +50798,7 @@
           <t>E | 305呎 (1房)
 $582万
 $19,066/呎
-(25年-09月)</t>
+(25年-09月-14日)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -50829,7 +50829,7 @@
           <t>A | 439呎 (2房)
 $1173万
 $26,715/呎
-(26年-06月)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -50845,7 +50845,7 @@
           <t>C | 244呎 (开放式)
 $496万
 $20,340/呎
-(26年-04月)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -50853,7 +50853,7 @@
           <t>D | 305呎 (1房)
 $546万
 $17,911/呎
-(25年-07月)</t>
+(25年-07月-29日)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -50861,7 +50861,7 @@
           <t>E | 305呎 (1房)
 $576万
 $18,869/呎
-(25年-09月)</t>
+(25年-09月-22日)</t>
         </is>
       </c>
       <c r="G26" s="22" t="inlineStr">
@@ -50877,7 +50877,7 @@
           <t>G | 494呎 (2房)
 $1162万
 $23,518/呎
-(25年-10月)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
     </row>
@@ -50916,7 +50916,7 @@
           <t>D | 305呎 (1房)
 $540万
 $17,715/呎
-(25年-08月)</t>
+(25年-08月-19日)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -50924,7 +50924,7 @@
           <t>E | 305呎 (1房)
 $559万
 $18,325/呎
-(25年-09月)</t>
+(25年-09月-08日)</t>
         </is>
       </c>
       <c r="G27" s="22" t="inlineStr">
@@ -50979,7 +50979,7 @@
           <t>D | 305呎 (1房)
 $534万
 $17,521/呎
-(25年-07月)</t>
+(25年-07月-21日)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -50987,7 +50987,7 @@
           <t>E | 305呎 (1房)
 $577万
 $18,931/呎
-(25年-10月)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="G28" s="22" t="inlineStr">
@@ -51042,7 +51042,7 @@
           <t>D | 305呎 (1房)
 $524万
 $17,174/呎
-(25年-07月)</t>
+(25年-07月-23日)</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
@@ -51050,7 +51050,7 @@
           <t>E | 305呎 (1房)
 $570万
 $18,685/呎
-(25年-10月)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="G29" s="22" t="inlineStr">
@@ -51222,7 +51222,7 @@
           <t>A | 593呎 (3房)
 $1658万
 $27,966/呎
-(25年-01月)</t>
+(25年-01月-01日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -51230,7 +51230,7 @@
           <t>B | 306呎 (1房)
 $662万
 $21,631/呎
-(25年-01月)</t>
+(25年-01月-01日)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -51238,7 +51238,7 @@
           <t>C | 447呎 (2房)
 $1010万
 $22,591/呎
-(25年-01月)</t>
+(25年-01月-01日)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -51246,7 +51246,7 @@
           <t>D | 1770呎 (4+房)
 $7080万
 $40,000/呎
-(25年-01月)</t>
+(25年-01月-06日)</t>
         </is>
       </c>
       <c r="F5" s="25" t="inlineStr"/>
@@ -51312,7 +51312,7 @@
           <t>G | 657呎 (3房)
 $1854万
 $28,221/呎
-(25年-01月)</t>
+(25年-01月-15日)</t>
         </is>
       </c>
     </row>
@@ -51493,7 +51493,7 @@
           <t>F | 705呎 (3房)
 $2185万
 $30,987/呎
-(25年-12月)</t>
+(25年-12月-22日)</t>
         </is>
       </c>
       <c r="H9" s="21" t="inlineStr">
@@ -51548,7 +51548,7 @@
           <t>E | 496呎 (2房)
 $1480万
 $29,829/呎
-(26年-07月)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -51556,7 +51556,7 @@
           <t>F | 705呎 (3房)
 $2207万
 $31,308/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="H10" s="21" t="inlineStr">
@@ -51619,7 +51619,7 @@
           <t>F | 705呎 (3房)
 $1946万
 $27,596/呎
-(25年-12月)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
       <c r="H11" s="21" t="inlineStr">
@@ -51674,7 +51674,7 @@
           <t>E | 496呎 (2房)
 $1366万
 $27,546/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
@@ -51682,7 +51682,7 @@
           <t>F | 705呎 (3房)
 $1936万
 $27,460/呎
-(25年-12月)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="H12" s="21" t="inlineStr">
@@ -51871,7 +51871,7 @@
           <t>F | 705呎 (3房)
 $2153万
 $30,538/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -51879,7 +51879,7 @@
           <t>G | 658呎 (3房)
 $2060万
 $31,301/呎
-(26年-07月)</t>
+(26年-07月-05日)</t>
         </is>
       </c>
     </row>
@@ -51997,7 +51997,7 @@
           <t>F | 705呎 (3房)
 $2192万
 $31,085/呎
-(26年-06月)</t>
+(26年-06月-21日)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -52005,7 +52005,7 @@
           <t>G | 658呎 (3房)
 $1995万
 $30,322/呎
-(26年-06月)</t>
+(26年-06月-21日)</t>
         </is>
       </c>
     </row>
@@ -52052,7 +52052,7 @@
           <t>E | 496呎 (2房)
 $1326万
 $26,736/呎
-(26年-03月)</t>
+(26年-03月-04日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -52060,7 +52060,7 @@
           <t>F | 705呎 (3房)
 $1879万
 $26,648/呎
-(25年-04月)</t>
+(25年-04月-27日)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -52068,7 +52068,7 @@
           <t>G | 658呎 (3房)
 $1933万
 $29,372/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
     </row>
@@ -52107,7 +52107,7 @@
           <t>D | 447呎 (2房)
 $1099万
 $24,586/呎
-(26年-03月)</t>
+(26年-03月-05日)</t>
         </is>
       </c>
       <c r="F19" s="24" t="inlineStr">
@@ -52123,7 +52123,7 @@
           <t>F | 705呎 (3房)
 $2110万
 $29,933/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="H19" s="21" t="inlineStr">
@@ -52186,7 +52186,7 @@
           <t>F | 705呎 (3房)
 $1860万
 $26,383/呎
-(25年-11月)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="H20" s="21" t="inlineStr">
@@ -52249,7 +52249,7 @@
           <t>F | 705呎 (3房)
 $1892万
 $26,834/呎
-(25年-06月)</t>
+(25年-06月-11日)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -52257,7 +52257,7 @@
           <t>G | 658呎 (3房)
 $1904万
 $28,935/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
     </row>
@@ -52312,7 +52312,7 @@
           <t>F | 705呎 (3房)
 $1841万
 $26,119/呎
-(25年-07月)</t>
+(25年-07月-26日)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -52320,7 +52320,7 @@
           <t>G | 658呎 (3房)
 $1678万
 $25,503/呎
-(25年-12月)</t>
+(25年-12月-02日)</t>
         </is>
       </c>
     </row>
@@ -52548,7 +52548,7 @@
           <t>D | 447呎 (2房)
 $1053万
 $23,548/呎
-(26年-03月)</t>
+(26年-03月-15日)</t>
         </is>
       </c>
       <c r="F26" s="24" t="inlineStr">
@@ -52564,7 +52564,7 @@
           <t>F | 705呎 (3房)
 $2122万
 $30,104/呎
-(26年-06月)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="H26" s="24" t="inlineStr">
@@ -52611,7 +52611,7 @@
           <t>D | 447呎 (2房)
 $1042万
 $23,300/呎
-(26年-03月)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
       <c r="F27" s="24" t="inlineStr">

--- a/files/九龙-启德-维港．双钻.xlsx
+++ b/files/九龙-启德-维港．双钻.xlsx
@@ -7763,7 +7763,7 @@
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>16.25%</t>
         </is>
       </c>
       <c r="K115" s="5" t="n">
